--- a/문서함/DB/리소스.xlsx
+++ b/문서함/DB/리소스.xlsx
@@ -8,6 +8,9 @@
     <sheet state="visible" name="기술 카드 리소스" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="파워 카드 리소스" sheetId="4" r:id="rId8"/>
     <sheet state="visible" name="카드 용어상태효과 리스트" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="object_Base_Table" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="chunk_Table" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="map_Theme_Table" sheetId="8" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -15,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="468">
   <si>
     <t>No.</t>
   </si>
@@ -527,9 +530,6 @@
     <t>바람을 날카롭게 가르는 소리 "슉!"</t>
   </si>
   <si>
-    <t>대기</t>
-  </si>
-  <si>
     <t>SND_MOV_Dash_End</t>
   </si>
   <si>
@@ -623,7 +623,7 @@
     <t>약 0.3s</t>
   </si>
   <si>
-    <t>바닥에 끌리다 멈추는 소라 "드르륵- 쾅!"</t>
+    <t>바닥에 끌리다 멈추는 소리 "드르륵- 쾅!"</t>
   </si>
   <si>
     <t>카드 이름</t>
@@ -671,10 +671,10 @@
     <t>인접 1칸</t>
   </si>
   <si>
-    <t>인접한 적 하나에게 6의 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t>피해를 6 줍니다.</t>
+    <t>인접한 적 하나에게 1의 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t>피해를 2 줍니다.</t>
   </si>
   <si>
     <t>찌르기</t>
@@ -686,10 +686,7 @@
     <t>눈꽃 2칸</t>
   </si>
   <si>
-    <t>직선 방향으로 2칸 내의 모든 적을 꿰뚫어 8의 피해를 줍니다. 벽에 막히면 그 뒤는 공격할 수 없습니다.</t>
-  </si>
-  <si>
-    <t>피해를 8 줍니다.</t>
+    <t>직선 방향으로 2칸 내의 모든 적을 꿰뚫어 2의 피해를 줍니다. 벽에 막히면 그 뒤는 공격할 수 없습니다.</t>
   </si>
   <si>
     <t>어깨치기</t>
@@ -701,7 +698,7 @@
     <t>인접한 타일 중 한칸으로 돌진한 뒤, 바로 앞의 적에게 6의 피해를 줍니다.</t>
   </si>
   <si>
-    <t>1 칸 이동 후 바로 앞 적에게 피해 6을 줍니다.</t>
+    <t>1 칸 이동 후 바로 앞 적에게 피해 2을 줍니다.</t>
   </si>
   <si>
     <t>휩쓸기</t>
@@ -713,7 +710,7 @@
     <t>전방 3칸 범위의 모든 적에게 5의 피해를 주고 1칸 뒤로 밀쳐냅니다. 밀려난 위치에 장애물이 있으면 추가 피해를 줍니다.</t>
   </si>
   <si>
-    <t>피해를 5 줍니다. \n피격된 적은 넉백을 받습니다.</t>
+    <t>피해를 1 줍니다. \n피격된 적은 넉백을 받습니다.</t>
   </si>
   <si>
     <t>처형</t>
@@ -737,7 +734,7 @@
     <t>인접한 적에게 6의 피해를 주고, 입힌 피해량만큼 자신의 [방어도]를 올립니다.</t>
   </si>
   <si>
-    <t>피해를 6 줍니다. \n입힌 피해량만큼 [방어도]를 얻습니다.</t>
+    <t>피해를 2 줍니다. \n입힌 피해량만큼 [방어도]를 얻습니다.</t>
   </si>
   <si>
     <t>회전 베기</t>
@@ -761,195 +758,195 @@
     <t>2칸 내의 적 하나에게 5의 피해를 줍니다. 벽 너머의 적도 공격할 수 있습니다.</t>
   </si>
   <si>
-    <t xml:space="preserve">피해를 5 줍니다. </t>
+    <t xml:space="preserve">피해를 1 줍니다. </t>
   </si>
   <si>
     <t>정밀 사격</t>
   </si>
   <si>
+    <t>적에게 6의 피해를 주고, 1턴 동안 받는 피해가 50% 증가하는 [표적] 상태로 만듭니다.</t>
+  </si>
+  <si>
+    <t>관통 화살</t>
+  </si>
+  <si>
+    <t>투사/관통</t>
+  </si>
+  <si>
+    <t>눈꽃 방향(가로, 세로, 대각선 8방향) 2칸 내의 모든 적에게 6의 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t>피해를 1 줍니다.</t>
+  </si>
+  <si>
+    <t>그림자 묶기</t>
+  </si>
+  <si>
+    <t>고립 1</t>
+  </si>
+  <si>
+    <t>적에게 5의 피해를 주고 1턴 동안 이동할 수 없는 [고립] 상태로 만듭니다.</t>
+  </si>
+  <si>
+    <t>피해를 5 줍니다. \n[고립 1]을 부여합니다.</t>
+  </si>
+  <si>
+    <t>마력 폭탄</t>
+  </si>
+  <si>
+    <t>투사/폭팔</t>
+  </si>
+  <si>
+    <t>대상에게 10의 피해를 주고, 주변 X자 범위에 5의 스플래시 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t>피해를 2 줍니다. \n주변 타일에 피해를 1 줍니다.</t>
+  </si>
+  <si>
+    <t>견제 사격</t>
+  </si>
+  <si>
+    <t>다음 인접 카드 50% 증가</t>
+  </si>
+  <si>
+    <t>8방향 2칸 내의 모든 적에게 4의 피해와 [고립]을 부여합니다. 사용 후 다음에 쓰는 [인접] 카드의 피해량이 50% 증가합니다.</t>
+  </si>
+  <si>
+    <t>피해를 4 줍니다. \n[고립 1]을 부여하고 다음에 사용하는 [인접] 카드의 피해량이 50% 증가합니다.</t>
+  </si>
+  <si>
+    <t>육중한 압박</t>
+  </si>
+  <si>
+    <t>방어도 * 1.5</t>
+  </si>
+  <si>
+    <t>인접한 적에게 현재 내 [방어도] 수치의 1.5배만큼 피해를 줍니다. (방어도는 소모되지 않음)</t>
+  </si>
+  <si>
+    <t>방어도 x 1.5의 피해를 줍니다. \n(피해를 n 줍니다.)</t>
+  </si>
+  <si>
+    <t>구석 몰이</t>
+  </si>
+  <si>
+    <t>인접한 적에게 4의 피해를 줍니다. 적의 뒤가 벽이나 다른 개체로 막혀 있다면 8의 추가 피해를 입힙니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피해를 4 줍니다. \n적 뒤에 막혀 있다면 </t>
+  </si>
+  <si>
+    <t>궁지 타격</t>
+  </si>
+  <si>
+    <t>인접한 적에게 7의 피해를 줍니다. 대상의 뒤가 벽이라면 코스트가 0이 됩니다.</t>
+  </si>
+  <si>
+    <t>피해를 7 줍니다. \n적 뒤가 벽이라면 코스트가 0이됩니다.</t>
+  </si>
+  <si>
+    <t>불도저</t>
+  </si>
+  <si>
+    <t>지정 방향으로 2칸 돌진하며 경로상의 적을 밀어내고 4+4의 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t>낡은 방패</t>
+  </si>
+  <si>
+    <t>방어</t>
+  </si>
+  <si>
+    <t>본인</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>방어도 5</t>
+  </si>
+  <si>
+    <t>즉시 1의 [방어도]를 얻습니다.</t>
+  </si>
+  <si>
+    <t>무기 교체</t>
+  </si>
+  <si>
+    <t>방어도 4</t>
+  </si>
+  <si>
+    <t>즉시 1의 [방어도]를 얻고, 버린 카드 더미에서 원하는 카드 1장을 손패로 가져옵니다.</t>
+  </si>
+  <si>
+    <t>패링</t>
+  </si>
+  <si>
+    <t>방어도 9</t>
+  </si>
+  <si>
+    <t>즉시 2의 [방어도]를 얻습니다. 턴 종료 시 사라지지 않고 손패에 유지됩니다.</t>
+  </si>
+  <si>
+    <t>맹독의 늪</t>
+  </si>
+  <si>
+    <t>영역/디버프</t>
+  </si>
+  <si>
+    <t>턴 당 3</t>
+  </si>
+  <si>
+    <t>3턴 동안 유지되는 독 장판을 생성합니다. 진입 시 4, 매 턴 3의 피해를 주며 적을 [혼란] 상태로 만듭니다.</t>
+  </si>
+  <si>
+    <t>타오르는 잿불</t>
+  </si>
+  <si>
+    <t>영역/피해</t>
+  </si>
+  <si>
+    <t>턴 당 8</t>
+  </si>
+  <si>
+    <t>2턴 동안 강력한 불길을 일으켜 진입 및 턴 시작 시 8의 피해를 줍니다.</t>
+  </si>
+  <si>
+    <t>거미줄 함정</t>
+  </si>
+  <si>
+    <t>영역/CC</t>
+  </si>
+  <si>
+    <t>밟으면 파괴되며 즉시 대상을 [고립] 상태로 만드는 함정을 설치합니다.</t>
+  </si>
+  <si>
+    <t>성역의 문양</t>
+  </si>
+  <si>
+    <t>영역/버프</t>
+  </si>
+  <si>
+    <t>3턴 동안 유지되는 문양을 새깁니다. 플레이어가 이 위를 밟으면 5의 [방어도]를 얻습니다.</t>
+  </si>
+  <si>
+    <t>빛의 웅덩이</t>
+  </si>
+  <si>
+    <t>5 회복, 집중 1</t>
+  </si>
+  <si>
+    <t>2턴 동안 유지되는 빛의 영역을 만듭니다. 이 위에서 턴을 시작하거나 진입 시 체력을 5 회복하고 [집중] 상태가 됩니다.</t>
+  </si>
+  <si>
+    <t>약점 분석</t>
+  </si>
+  <si>
+    <t>디버프</t>
+  </si>
+  <si>
     <t>표적 1</t>
   </si>
   <si>
-    <t>적에게 6의 피해를 주고, 1턴 동안 받는 피해가 50% 증가하는 [표적] 상태로 만듭니다.</t>
-  </si>
-  <si>
-    <t>피해를 6 줍니다. \n[표적 1]을 부여합니다.</t>
-  </si>
-  <si>
-    <t>관통 화살</t>
-  </si>
-  <si>
-    <t>투사/관통</t>
-  </si>
-  <si>
-    <t>눈꽃 방향(가로, 세로, 대각선 8방향) 2칸 내의 모든 적에게 6의 피해를 주고 [표적] 상태를 부여합니다.</t>
-  </si>
-  <si>
-    <t>그림자 묶기</t>
-  </si>
-  <si>
-    <t>고립 1</t>
-  </si>
-  <si>
-    <t>적에게 5의 피해를 주고 1턴 동안 이동할 수 없는 [고립] 상태로 만듭니다.</t>
-  </si>
-  <si>
-    <t>피해를 5 줍니다. \n[고립 1]을 부여합니다.</t>
-  </si>
-  <si>
-    <t>마력 폭탄</t>
-  </si>
-  <si>
-    <t>투사/폭팔</t>
-  </si>
-  <si>
-    <t>대상에게 10의 피해를 주고, 주변 X자 범위에 5의 스플래시 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t>피해를 10 줍니다. \n주변 타일에 피해를 5 줍니다.</t>
-  </si>
-  <si>
-    <t>견제 사격</t>
-  </si>
-  <si>
-    <t>다음 인접 카드 50% 증가</t>
-  </si>
-  <si>
-    <t>8방향 2칸 내의 모든 적에게 4의 피해와 [고립]을 부여합니다. 사용 후 다음에 쓰는 [인접] 카드의 피해량이 50% 증가합니다.</t>
-  </si>
-  <si>
-    <t>피해를 4 줍니다. \n[고립 1]을 부여하고 다음에 사용하는 [인접] 카드의 피해량이 50% 증가합니다.</t>
-  </si>
-  <si>
-    <t>육중한 압박</t>
-  </si>
-  <si>
-    <t>방어도 * 1.5</t>
-  </si>
-  <si>
-    <t>인접한 적에게 현재 내 [방어도] 수치의 1.5배만큼 피해를 줍니다. (방어도는 소모되지 않음)</t>
-  </si>
-  <si>
-    <t>방어도 x 1.5의 피해를 줍니다. \n(피해를 n 줍니다.)</t>
-  </si>
-  <si>
-    <t>구석 몰이</t>
-  </si>
-  <si>
-    <t>인접한 적에게 4의 피해를 줍니다. 적의 뒤가 벽이나 다른 개체로 막혀 있다면 8의 추가 피해를 입힙니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">피해를 4 줍니다. \n적 뒤에 막혀 있다면 </t>
-  </si>
-  <si>
-    <t>궁지 타격</t>
-  </si>
-  <si>
-    <t>인접한 적에게 7의 피해를 줍니다. 대상의 뒤가 벽이라면 코스트가 0이 됩니다.</t>
-  </si>
-  <si>
-    <t>피해를 7 줍니다. \n적 뒤가 벽이라면 코스트가 0이됩니다.</t>
-  </si>
-  <si>
-    <t>불도저</t>
-  </si>
-  <si>
-    <t>지정 방향으로 2칸 돌진하며 경로상의 적을 밀어내고 4+4의 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t>낡은 방패</t>
-  </si>
-  <si>
-    <t>방어</t>
-  </si>
-  <si>
-    <t>본인</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>방어도 5</t>
-  </si>
-  <si>
-    <t>즉시 5의 [방어도]를 얻습니다.</t>
-  </si>
-  <si>
-    <t>무기 교체</t>
-  </si>
-  <si>
-    <t>방어도 4</t>
-  </si>
-  <si>
-    <t>즉시 4의 [방어도]를 얻고, 버린 카드 더미에서 원하는 카드 1장을 손패로 가져옵니다.</t>
-  </si>
-  <si>
-    <t>패링</t>
-  </si>
-  <si>
-    <t>방어도 9</t>
-  </si>
-  <si>
-    <t>즉시 9의 [방어도]를 얻습니다. 턴 종료 시 사라지지 않고 손패에 유지됩니다.</t>
-  </si>
-  <si>
-    <t>맹독의 늪</t>
-  </si>
-  <si>
-    <t>영역/디버프</t>
-  </si>
-  <si>
-    <t>턴 당 3</t>
-  </si>
-  <si>
-    <t>3턴 동안 유지되는 독 장판을 생성합니다. 진입 시 4, 매 턴 3의 피해를 주며 적을 [혼란] 상태로 만듭니다.</t>
-  </si>
-  <si>
-    <t>타오르는 잿불</t>
-  </si>
-  <si>
-    <t>영역/피해</t>
-  </si>
-  <si>
-    <t>턴 당 8</t>
-  </si>
-  <si>
-    <t>2턴 동안 강력한 불길을 일으켜 진입 및 턴 시작 시 8의 피해를 줍니다.</t>
-  </si>
-  <si>
-    <t>거미줄 함정</t>
-  </si>
-  <si>
-    <t>영역/CC</t>
-  </si>
-  <si>
-    <t>밟으면 파괴되며 즉시 대상을 [고립] 상태로 만드는 함정을 설치합니다.</t>
-  </si>
-  <si>
-    <t>성역의 문양</t>
-  </si>
-  <si>
-    <t>영역/버프</t>
-  </si>
-  <si>
-    <t>3턴 동안 유지되는 문양을 새깁니다. 플레이어가 이 위를 밟으면 5의 [방어도]를 얻습니다.</t>
-  </si>
-  <si>
-    <t>빛의 웅덩이</t>
-  </si>
-  <si>
-    <t>5 회복, 집중 1</t>
-  </si>
-  <si>
-    <t>2턴 동안 유지되는 빛의 영역을 만듭니다. 이 위에서 턴을 시작하거나 진입 시 체력을 5 회복하고 [집중] 상태가 됩니다.</t>
-  </si>
-  <si>
-    <t>약점 분석</t>
-  </si>
-  <si>
-    <t>디버프</t>
-  </si>
-  <si>
     <t>적에게 [표적 1] 상태를 부여합니다.</t>
   </si>
   <si>
@@ -1028,7 +1025,7 @@
     <t>방어도 2</t>
   </si>
   <si>
-    <t>인접한 빈칸으로 이동하고 2의 [방어도]를 얻습니다.</t>
+    <t>인접한 1칸 이동하고 1의 [방어도]를 얻습니다.</t>
   </si>
   <si>
     <t>압사</t>
@@ -1263,6 +1260,168 @@
   </si>
   <si>
     <t>덱 빌드를 방해하는 카드를 카드 더미에 넣어 플레이어의 드로우 기회를 박탈합니다.</t>
+  </si>
+  <si>
+    <t>object_Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name </t>
+  </si>
+  <si>
+    <t xml:space="preserve">type </t>
+  </si>
+  <si>
+    <t xml:space="preserve">heath </t>
+  </si>
+  <si>
+    <t>damge</t>
+  </si>
+  <si>
+    <t>Is_Passable</t>
+  </si>
+  <si>
+    <t>고유 아이디</t>
+  </si>
+  <si>
+    <t>구분 이름</t>
+  </si>
+  <si>
+    <t>체력( - 은 체력 없음)</t>
+  </si>
+  <si>
+    <t>피해량 ( - 은 체력 없음)</t>
+  </si>
+  <si>
+    <t>BFS 검사 시 통과 여부</t>
+  </si>
+  <si>
+    <t>빈칸</t>
+  </si>
+  <si>
+    <t>Empty</t>
+  </si>
+  <si>
+    <t>이끼낀 외벽</t>
+  </si>
+  <si>
+    <t>Unbr</t>
+  </si>
+  <si>
+    <t>부서진 외벽</t>
+  </si>
+  <si>
+    <t>벽 횃불</t>
+  </si>
+  <si>
+    <t>철창</t>
+  </si>
+  <si>
+    <t>석관</t>
+  </si>
+  <si>
+    <t>가시 함정</t>
+  </si>
+  <si>
+    <t>폭탄</t>
+  </si>
+  <si>
+    <t>비석</t>
+  </si>
+  <si>
+    <t>Br</t>
+  </si>
+  <si>
+    <t>보물상자</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chunk_Id </t>
+  </si>
+  <si>
+    <t>chunk_Size</t>
+  </si>
+  <si>
+    <t>chunk_Data</t>
+  </si>
+  <si>
+    <t>descripts</t>
+  </si>
+  <si>
+    <t>청크 사이즈 (W x H)</t>
+  </si>
+  <si>
+    <t>청크 정보</t>
+  </si>
+  <si>
+    <t>2 x 2</t>
+  </si>
+  <si>
+    <t>101, 102 / 0, 101</t>
+  </si>
+  <si>
+    <t>3 x 1</t>
+  </si>
+  <si>
+    <t>105, 103, 102</t>
+  </si>
+  <si>
+    <t>3 x 3</t>
+  </si>
+  <si>
+    <t>101, 101, 101 / 104, 302, 104 / 0, 201, 0</t>
+  </si>
+  <si>
+    <t>1 x 3</t>
+  </si>
+  <si>
+    <t>102 / 202 / 102</t>
+  </si>
+  <si>
+    <t>3 x 2</t>
+  </si>
+  <si>
+    <t>101, 103, 101 / 0, 201, 0</t>
+  </si>
+  <si>
+    <t>201, 0 / 0, 202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theme_Id </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theme_name </t>
+  </si>
+  <si>
+    <t xml:space="preserve">global_Obstacle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chunk_Pool </t>
+  </si>
+  <si>
+    <t xml:space="preserve">object_Spawn_Data </t>
+  </si>
+  <si>
+    <t>고분 이름</t>
+  </si>
+  <si>
+    <t>오브젝트 총합 제한 (최소, 최대)</t>
+  </si>
+  <si>
+    <t>해당 테마 등장 청크 ID 목록</t>
+  </si>
+  <si>
+    <t>스폰 룰렛 데이터 [object_Id, spawn_Weight, max_Spawn_Limit]</t>
+  </si>
+  <si>
+    <t>버려진 성곽 (표준 맵)</t>
+  </si>
+  <si>
+    <t>13, 17</t>
+  </si>
+  <si>
+    <t>10001, 10002, 10003, 10004, 10005, 10006</t>
+  </si>
+  <si>
+    <t>101:30:5, 102:30:5, 201:15:3, 202:5:1</t>
   </si>
 </sst>
 </file>
@@ -1317,7 +1476,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1338,14 +1497,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB4A7D6"/>
+        <bgColor rgb="FFB4A7D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD5A6BD"/>
         <bgColor rgb="FFD5A6BD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor rgb="FFCCCCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1369,7 +1540,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="40">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1415,7 +1586,13 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1433,6 +1610,9 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -1443,6 +1623,38 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1541,6 +1753,18 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -2785,7 +3009,7 @@
         <v>169</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35">
@@ -2793,28 +3017,28 @@
         <v>33.0</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>165</v>
       </c>
       <c r="D35" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="F35" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="G35" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="F35" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="G35" s="6" t="s">
+      <c r="H35" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="H35" s="9" t="s">
-        <v>175</v>
-      </c>
       <c r="I35" s="6" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36">
@@ -2822,28 +3046,28 @@
         <v>34.0</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>165</v>
       </c>
       <c r="D36" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="F36" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H36" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F36" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>179</v>
-      </c>
       <c r="I36" s="6" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37">
@@ -2851,28 +3075,28 @@
         <v>35.0</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>165</v>
       </c>
       <c r="D37" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="F37" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F37" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="G37" s="6" t="s">
+      <c r="H37" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="H37" s="9" t="s">
-        <v>184</v>
-      </c>
       <c r="I37" s="6" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38">
@@ -2880,28 +3104,28 @@
         <v>36.0</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>165</v>
       </c>
       <c r="D38" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="F38" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F38" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="H38" s="9" t="s">
-        <v>189</v>
-      </c>
       <c r="I38" s="6" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
@@ -2909,28 +3133,28 @@
         <v>37.0</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>165</v>
       </c>
       <c r="D39" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="F39" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="F39" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>193</v>
-      </c>
       <c r="I39" s="6" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
@@ -2938,28 +3162,28 @@
         <v>38.0</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>165</v>
       </c>
       <c r="D40" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="F40" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="F40" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>197</v>
-      </c>
       <c r="I40" s="6" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
@@ -2967,28 +3191,28 @@
         <v>39.0</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>165</v>
       </c>
       <c r="D41" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="F41" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="G41" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F41" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="G41" s="6" t="s">
+      <c r="H41" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>202</v>
-      </c>
       <c r="I41" s="6" t="s">
-        <v>170</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
@@ -3029,7 +3253,9 @@
     </row>
     <row r="45">
       <c r="A45" s="10"/>
-      <c r="B45" s="6"/>
+      <c r="B45" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="C45" s="6"/>
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
@@ -3700,40 +3926,40 @@
         <v>9</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="7" t="s">
         <v>213</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="2">
@@ -3741,13 +3967,13 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="14" t="s">
         <v>216</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>217</v>
       </c>
       <c r="E2" s="12">
         <v>1.0</v>
@@ -3764,11 +3990,11 @@
       </c>
       <c r="J2" s="14"/>
       <c r="K2" s="14"/>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="3">
@@ -3776,13 +4002,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="D3" s="16" t="s">
         <v>221</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>222</v>
       </c>
       <c r="E3" s="12">
         <v>1.0</v>
@@ -3799,25 +4025,25 @@
       </c>
       <c r="J3" s="14"/>
       <c r="K3" s="14"/>
-      <c r="L3" s="14" t="s">
-        <v>223</v>
+      <c r="L3" s="15" t="s">
+        <v>222</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12">
         <v>3.0</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>225</v>
+      <c r="B4" s="17" t="s">
+        <v>223</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E4" s="12">
         <v>1.0</v>
@@ -3835,10 +4061,10 @@
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
       <c r="L4" s="14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5">
@@ -3846,13 +4072,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E5" s="12">
         <v>2.0</v>
@@ -3869,27 +4095,27 @@
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>230</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12">
         <v>5.0</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>233</v>
+      <c r="B6" s="17" t="s">
+        <v>231</v>
       </c>
       <c r="C6" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>216</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>217</v>
       </c>
       <c r="E6" s="12">
         <v>1.0</v>
@@ -3905,14 +4131,14 @@
         <v>15.0</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K6" s="14"/>
       <c r="L6" s="14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7">
@@ -3920,13 +4146,13 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C7" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>216</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>217</v>
       </c>
       <c r="E7" s="12">
         <v>1.0</v>
@@ -3942,14 +4168,14 @@
         <v>6.0</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K7" s="14"/>
       <c r="L7" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8">
@@ -3957,13 +4183,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E8" s="12">
         <v>2.0</v>
@@ -3981,10 +4207,10 @@
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
       <c r="L8" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9">
@@ -3992,13 +4218,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>244</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>246</v>
       </c>
       <c r="E9" s="12">
         <v>1.0</v>
@@ -4016,24 +4242,24 @@
       <c r="J9" s="14"/>
       <c r="K9" s="14"/>
       <c r="L9" s="14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12">
         <v>9.0</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>249</v>
+      <c r="B10" s="17" t="s">
+        <v>247</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E10" s="12">
         <v>1.0</v>
@@ -4049,28 +4275,26 @@
         <v>6.0</v>
       </c>
       <c r="J10" s="14"/>
-      <c r="K10" s="14" t="s">
-        <v>250</v>
-      </c>
+      <c r="K10" s="14"/>
       <c r="L10" s="14" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12">
         <v>10.0</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>253</v>
+      <c r="B11" s="17" t="s">
+        <v>249</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>222</v>
+        <v>250</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>221</v>
       </c>
       <c r="E11" s="12">
         <v>1.0</v>
@@ -4086,11 +4310,9 @@
         <v>6.0</v>
       </c>
       <c r="J11" s="14"/>
-      <c r="K11" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>255</v>
+      <c r="K11" s="14"/>
+      <c r="L11" s="15" t="s">
+        <v>251</v>
       </c>
       <c r="M11" s="7" t="s">
         <v>252</v>
@@ -4100,14 +4322,14 @@
       <c r="A12" s="12">
         <v>11.0</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>256</v>
+      <c r="B12" s="17" t="s">
+        <v>253</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E12" s="12">
         <v>1.0</v>
@@ -4124,13 +4346,13 @@
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="14" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13">
@@ -4138,13 +4360,13 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>246</v>
+        <v>258</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>244</v>
       </c>
       <c r="E13" s="12">
         <v>2.0</v>
@@ -4156,30 +4378,30 @@
       <c r="H13" s="12">
         <v>5.0</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="18">
         <v>46300.0</v>
       </c>
       <c r="J13" s="14"/>
       <c r="K13" s="14"/>
       <c r="L13" s="14" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12">
         <v>13.0</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>264</v>
+      <c r="B14" s="17" t="s">
+        <v>261</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>222</v>
+        <v>250</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>221</v>
       </c>
       <c r="E14" s="12">
         <v>1.0</v>
@@ -4195,16 +4417,16 @@
         <v>4.0</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15">
@@ -4212,13 +4434,13 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C15" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" s="14" t="s">
         <v>216</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>217</v>
       </c>
       <c r="E15" s="12">
         <v>1.0</v>
@@ -4231,15 +4453,15 @@
         <v>1.0</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="J15" s="14"/>
       <c r="K15" s="14"/>
       <c r="L15" s="14" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16">
@@ -4247,13 +4469,13 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C16" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>216</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>217</v>
       </c>
       <c r="E16" s="12">
         <v>1.0</v>
@@ -4265,16 +4487,16 @@
       <c r="H16" s="12">
         <v>1.0</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="18">
         <v>46120.0</v>
       </c>
       <c r="J16" s="14"/>
       <c r="K16" s="14"/>
       <c r="L16" s="14" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17">
@@ -4282,13 +4504,13 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C17" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" s="14" t="s">
         <v>216</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>217</v>
       </c>
       <c r="E17" s="12">
         <v>1.0</v>
@@ -4303,13 +4525,13 @@
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
       <c r="K17" s="14" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18">
@@ -4317,13 +4539,13 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E18" s="12">
         <v>2.0</v>
@@ -4340,20 +4562,20 @@
       </c>
       <c r="J18" s="14"/>
       <c r="K18" s="14" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -4377,37 +4599,37 @@
         <v>9</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>212</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="2">
@@ -4415,35 +4637,35 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="E2" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="G2" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="K2" s="14"/>
+      <c r="L2" s="15" t="s">
         <v>282</v>
-      </c>
-      <c r="E2" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="G2" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="3">
@@ -4451,35 +4673,35 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="E3" s="17">
+        <v>279</v>
+      </c>
+      <c r="E3" s="19">
         <v>0.0</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G3" s="12">
         <v>1.0</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K3" s="14"/>
-      <c r="L3" s="14" t="s">
-        <v>288</v>
+      <c r="L3" s="15" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="4">
@@ -4487,49 +4709,49 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E4" s="12">
         <v>1.0</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G4" s="12">
         <v>1.0</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="K4" s="14"/>
-      <c r="L4" s="14" t="s">
-        <v>291</v>
+      <c r="L4" s="15" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12">
         <v>4.0</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>292</v>
+      <c r="B5" s="17" t="s">
+        <v>289</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E5" s="12">
         <v>1.0</v>
@@ -4544,28 +4766,28 @@
         <v>1.0</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="J5" s="14"/>
       <c r="K5" s="14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12">
         <v>5.0</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>296</v>
+      <c r="B6" s="17" t="s">
+        <v>293</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E6" s="12">
         <v>2.0</v>
@@ -4580,26 +4802,26 @@
         <v>1.0</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
       <c r="L6" s="14" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12">
         <v>6.0</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>300</v>
+      <c r="B7" s="17" t="s">
+        <v>297</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E7" s="12">
         <v>1.0</v>
@@ -4618,24 +4840,24 @@
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="14" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12">
         <v>7.0</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>303</v>
+      <c r="B8" s="17" t="s">
+        <v>300</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E8" s="12">
         <v>1.0</v>
@@ -4653,25 +4875,25 @@
         <v>0.0</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="K8" s="14"/>
       <c r="L8" s="14" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12">
         <v>8.0</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>306</v>
+      <c r="B9" s="17" t="s">
+        <v>303</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E9" s="12">
         <v>2.0</v>
@@ -4689,27 +4911,27 @@
         <v>0.0</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="K9" s="14"/>
       <c r="L9" s="14" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12">
         <v>9.0</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>309</v>
+      <c r="B10" s="17" t="s">
+        <v>306</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="E10" s="18">
+        <v>244</v>
+      </c>
+      <c r="E10" s="20">
         <v>1.0</v>
       </c>
       <c r="F10" s="12">
@@ -4726,26 +4948,26 @@
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="14" t="s">
-        <v>250</v>
+        <v>308</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12">
         <v>10.0</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>312</v>
+      <c r="B11" s="17" t="s">
+        <v>310</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="E11" s="18">
+        <v>244</v>
+      </c>
+      <c r="E11" s="20">
         <v>1.0</v>
       </c>
       <c r="F11" s="12">
@@ -4762,26 +4984,26 @@
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12">
         <v>11.0</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>314</v>
+      <c r="B12" s="17" t="s">
+        <v>312</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="E12" s="18">
+        <v>244</v>
+      </c>
+      <c r="E12" s="20">
         <v>2.0</v>
       </c>
       <c r="F12" s="12">
@@ -4798,26 +5020,26 @@
       </c>
       <c r="J12" s="14"/>
       <c r="K12" s="14" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12">
         <v>12.0</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>317</v>
+      <c r="B13" s="17" t="s">
+        <v>315</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="E13" s="18">
+        <v>244</v>
+      </c>
+      <c r="E13" s="20">
         <v>1.0</v>
       </c>
       <c r="F13" s="12">
@@ -4830,37 +5052,37 @@
         <v>1.0</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J13" s="14"/>
       <c r="K13" s="14" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12">
         <v>13.0</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>321</v>
+      <c r="B14" s="17" t="s">
+        <v>319</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="E14" s="18">
+        <v>244</v>
+      </c>
+      <c r="E14" s="20">
         <v>1.0</v>
       </c>
       <c r="F14" s="12">
         <v>2.0</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H14" s="12">
         <v>1.0</v>
@@ -4870,30 +5092,30 @@
       </c>
       <c r="J14" s="14"/>
       <c r="K14" s="14" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12">
         <v>14.0</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>324</v>
+      <c r="B15" s="17" t="s">
+        <v>322</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="E15" s="18">
+        <v>244</v>
+      </c>
+      <c r="E15" s="20">
         <v>1.0</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G15" s="12">
         <v>2.0</v>
@@ -4906,82 +5128,82 @@
       </c>
       <c r="J15" s="14"/>
       <c r="K15" s="14" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12">
         <v>15.0</v>
       </c>
-      <c r="B16" s="13" t="s">
-        <v>327</v>
+      <c r="B16" s="17" t="s">
+        <v>325</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="E16" s="18">
+        <v>279</v>
+      </c>
+      <c r="E16" s="20">
         <v>2.0</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G16" s="12">
         <v>1.0</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="K16" s="14"/>
       <c r="L16" s="14" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12">
         <v>16.0</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>329</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="E17" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="G17" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J17" s="14" t="s">
         <v>330</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>331</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="E17" s="18">
-        <v>1.0</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="G17" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>332</v>
       </c>
       <c r="K17" s="14"/>
       <c r="L17" s="14" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18">
@@ -4989,35 +5211,35 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="E18" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="H18" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J18" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="K18" s="14"/>
+      <c r="L18" s="15" t="s">
         <v>335</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="E18" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="F18" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="H18" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="J18" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="19">
@@ -5025,15 +5247,15 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="E19" s="18">
+        <v>244</v>
+      </c>
+      <c r="E19" s="20">
         <v>2.0</v>
       </c>
       <c r="F19" s="12">
@@ -5049,11 +5271,11 @@
         <v>0.0</v>
       </c>
       <c r="J19" s="14"/>
-      <c r="K19" s="19" t="s">
-        <v>339</v>
-      </c>
-      <c r="L19" s="20" t="s">
-        <v>340</v>
+      <c r="K19" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="L19" s="22" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="20">
@@ -5061,51 +5283,51 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="E20" s="20">
+        <v>1.0</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="L20" s="14" t="s">
         <v>341</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="E20" s="18">
-        <v>1.0</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="H20" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="I20" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="J20" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="L20" s="14" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7">
         <v>20.0</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>344</v>
+      <c r="B21" s="23" t="s">
+        <v>342</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E21" s="7">
         <v>1.0</v>
@@ -5114,26 +5336,21 @@
         <v>1.0</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="7" t="s">
-        <v>280</v>
+        <v>343</v>
       </c>
     </row>
     <row r="23">
       <c r="L23" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="25">
@@ -5141,12 +5358,12 @@
     </row>
     <row r="26">
       <c r="L26" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28">
       <c r="L28" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -5170,16 +5387,16 @@
         <v>9</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C1" s="11" t="s">
-        <v>204</v>
-      </c>
       <c r="D1" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2">
@@ -5187,16 +5404,16 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D2" s="12">
         <v>2.0</v>
       </c>
-      <c r="E2" s="20" t="s">
-        <v>351</v>
+      <c r="E2" s="22" t="s">
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -5216,317 +5433,317 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>353</v>
+      <c r="A1" s="24" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>351</v>
       </c>
       <c r="C1" s="14"/>
       <c r="D1" s="14" t="s">
+        <v>352</v>
+      </c>
+      <c r="E1" s="14"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>354</v>
-      </c>
-      <c r="E1" s="14"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>356</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>357</v>
       </c>
-      <c r="E2" s="22" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="21" t="s">
+      <c r="C3" s="14" t="s">
         <v>358</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>360</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="s">
-        <v>361</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>362</v>
+      <c r="A4" s="24" t="s">
+        <v>359</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>360</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
-        <v>363</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>364</v>
+      <c r="A5" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>362</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="s">
-        <v>365</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>366</v>
+      <c r="A6" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>364</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="s">
-        <v>367</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>368</v>
+      <c r="A7" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>366</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="s">
-        <v>238</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>369</v>
+      <c r="A8" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>367</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>371</v>
+      <c r="A9" s="24" t="s">
+        <v>368</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>369</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="s">
-        <v>372</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>373</v>
+      <c r="A10" s="24" t="s">
+        <v>370</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>371</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>374</v>
+      <c r="A11" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>372</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
       <c r="E11" s="14"/>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>376</v>
+      <c r="A12" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>374</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="s">
-        <v>377</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>378</v>
+      <c r="A13" s="26" t="s">
+        <v>375</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>376</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
       <c r="E13" s="14"/>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="s">
-        <v>379</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>380</v>
+      <c r="A14" s="26" t="s">
+        <v>377</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>378</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="24" t="s">
+        <v>379</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="s">
         <v>381</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B17" s="24" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="21" t="s">
+    <row r="18">
+      <c r="A18" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B18" s="24" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="21" t="s">
+    <row r="19">
+      <c r="A19" s="24" t="s">
         <v>385</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B19" s="24" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="21" t="s">
+    <row r="20">
+      <c r="A20" s="24" t="s">
         <v>387</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B20" s="24" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="21" t="s">
+    <row r="21">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="s">
         <v>389</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B22" s="24" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="21" t="s">
+    <row r="23">
+      <c r="A23" s="24" t="s">
         <v>391</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B23" s="24" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="21" t="s">
+    <row r="24">
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="s">
         <v>393</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B25" s="24" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="21"/>
-      <c r="B24" s="21"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="s">
+    <row r="26">
+      <c r="A26" s="24" t="s">
         <v>395</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B26" s="24" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="21" t="s">
+    <row r="27">
+      <c r="A27" s="24" t="s">
         <v>397</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B27" s="24" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="21" t="s">
+    <row r="28">
+      <c r="A28" s="24" t="s">
         <v>399</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B28" s="24" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="21" t="s">
+    <row r="29">
+      <c r="A29" s="24" t="s">
         <v>401</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B29" s="24" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="21" t="s">
+    <row r="30">
+      <c r="A30" s="24" t="s">
         <v>403</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B30" s="24" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="21" t="s">
+    <row r="32">
+      <c r="A32" s="24" t="s">
         <v>405</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B32" s="24" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="21" t="s">
+      <c r="B33" s="24" t="s">
         <v>407</v>
       </c>
-      <c r="B32" s="21" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="21" t="s">
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="s">
         <v>408</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B34" s="24" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="21" t="s">
+    <row r="35">
+      <c r="A35" s="24" t="s">
         <v>410</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B35" s="24" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="21" t="s">
+    <row r="36">
+      <c r="A36" s="24" t="s">
         <v>412</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B36" s="27" t="s">
         <v>413</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="s">
-        <v>414</v>
-      </c>
-      <c r="B36" s="24" t="s">
-        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -5535,4 +5752,6004 @@
   </hyperlinks>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="4" max="4" width="16.0"/>
+    <col customWidth="1" min="5" max="5" width="18.0"/>
+    <col customWidth="1" min="6" max="6" width="17.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="s">
+        <v>414</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>415</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>417</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>418</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>421</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>422</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>424</v>
+      </c>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F3" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7">
+        <v>101.0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F4" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7">
+        <v>102.0</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F5" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7">
+        <v>103.0</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F6" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7">
+        <v>104.0</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F7" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7">
+        <v>105.0</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F8" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7">
+        <v>201.0</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="F9" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7">
+        <v>202.0</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="F10" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7">
+        <v>301.0</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F11" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7">
+        <v>302.0</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="D12" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F12" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="15.88"/>
+    <col customWidth="1" min="3" max="3" width="27.88"/>
+    <col customWidth="1" min="4" max="4" width="25.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="s">
+        <v>438</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>441</v>
+      </c>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>442</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>443</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7">
+        <v>10001.0</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7">
+        <v>10002.0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7">
+        <v>10003.0</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7">
+        <v>10004.0</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7">
+        <v>10005.0</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7">
+        <v>10006.0</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>454</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="16.38"/>
+    <col customWidth="1" min="3" max="3" width="17.63"/>
+    <col customWidth="1" min="4" max="4" width="28.0"/>
+    <col customWidth="1" min="5" max="5" width="48.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="s">
+        <v>455</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>456</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>457</v>
+      </c>
+      <c r="D1" s="34" t="s">
+        <v>458</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>459</v>
+      </c>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="32" t="s">
+        <v>420</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>461</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>462</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>463</v>
+      </c>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="36"/>
+      <c r="Z2" s="36"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="37">
+        <v>1001.0</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>464</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>465</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>466</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>467</v>
+      </c>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="38"/>
+      <c r="V3" s="38"/>
+      <c r="W3" s="38"/>
+      <c r="X3" s="38"/>
+      <c r="Y3" s="38"/>
+      <c r="Z3" s="38"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="38"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="38"/>
+      <c r="U4" s="38"/>
+      <c r="V4" s="38"/>
+      <c r="W4" s="38"/>
+      <c r="X4" s="38"/>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="38"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="38"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="38"/>
+      <c r="T5" s="38"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="38"/>
+      <c r="W5" s="38"/>
+      <c r="X5" s="38"/>
+      <c r="Y5" s="38"/>
+      <c r="Z5" s="38"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="38"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="38"/>
+      <c r="T6" s="38"/>
+      <c r="U6" s="38"/>
+      <c r="V6" s="38"/>
+      <c r="W6" s="38"/>
+      <c r="X6" s="38"/>
+      <c r="Y6" s="38"/>
+      <c r="Z6" s="38"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="38"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="38"/>
+      <c r="V7" s="38"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="38"/>
+      <c r="Y7" s="38"/>
+      <c r="Z7" s="38"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="38"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="38"/>
+      <c r="Z8" s="38"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="38"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="38"/>
+      <c r="X9" s="38"/>
+      <c r="Y9" s="38"/>
+      <c r="Z9" s="38"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="38"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="38"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="38"/>
+      <c r="V10" s="38"/>
+      <c r="W10" s="38"/>
+      <c r="X10" s="38"/>
+      <c r="Y10" s="38"/>
+      <c r="Z10" s="38"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="38"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="38"/>
+      <c r="Y11" s="38"/>
+      <c r="Z11" s="38"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="38"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="38"/>
+      <c r="Y12" s="38"/>
+      <c r="Z12" s="38"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="38"/>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="38"/>
+      <c r="S13" s="38"/>
+      <c r="T13" s="38"/>
+      <c r="U13" s="38"/>
+      <c r="V13" s="38"/>
+      <c r="W13" s="38"/>
+      <c r="X13" s="38"/>
+      <c r="Y13" s="38"/>
+      <c r="Z13" s="38"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="38"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="38"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="38"/>
+      <c r="V14" s="38"/>
+      <c r="W14" s="38"/>
+      <c r="X14" s="38"/>
+      <c r="Y14" s="38"/>
+      <c r="Z14" s="38"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="38"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="38"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="38"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="38"/>
+      <c r="Y15" s="38"/>
+      <c r="Z15" s="38"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="38"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="38"/>
+      <c r="V16" s="38"/>
+      <c r="W16" s="38"/>
+      <c r="X16" s="38"/>
+      <c r="Y16" s="38"/>
+      <c r="Z16" s="38"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="38"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="38"/>
+      <c r="T17" s="38"/>
+      <c r="U17" s="38"/>
+      <c r="V17" s="38"/>
+      <c r="W17" s="38"/>
+      <c r="X17" s="38"/>
+      <c r="Y17" s="38"/>
+      <c r="Z17" s="38"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="38"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="38"/>
+      <c r="T18" s="38"/>
+      <c r="U18" s="38"/>
+      <c r="V18" s="38"/>
+      <c r="W18" s="38"/>
+      <c r="X18" s="38"/>
+      <c r="Y18" s="38"/>
+      <c r="Z18" s="38"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="38"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="38"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="38"/>
+      <c r="R19" s="38"/>
+      <c r="S19" s="38"/>
+      <c r="T19" s="38"/>
+      <c r="U19" s="38"/>
+      <c r="V19" s="38"/>
+      <c r="W19" s="38"/>
+      <c r="X19" s="38"/>
+      <c r="Y19" s="38"/>
+      <c r="Z19" s="38"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="38"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38"/>
+      <c r="S20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38"/>
+      <c r="W20" s="38"/>
+      <c r="X20" s="38"/>
+      <c r="Y20" s="38"/>
+      <c r="Z20" s="38"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="38"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="38"/>
+      <c r="V21" s="38"/>
+      <c r="W21" s="38"/>
+      <c r="X21" s="38"/>
+      <c r="Y21" s="38"/>
+      <c r="Z21" s="38"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="38"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="38"/>
+      <c r="R22" s="38"/>
+      <c r="S22" s="38"/>
+      <c r="T22" s="38"/>
+      <c r="U22" s="38"/>
+      <c r="V22" s="38"/>
+      <c r="W22" s="38"/>
+      <c r="X22" s="38"/>
+      <c r="Y22" s="38"/>
+      <c r="Z22" s="38"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="38"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="38"/>
+      <c r="R23" s="38"/>
+      <c r="S23" s="38"/>
+      <c r="T23" s="38"/>
+      <c r="U23" s="38"/>
+      <c r="V23" s="38"/>
+      <c r="W23" s="38"/>
+      <c r="X23" s="38"/>
+      <c r="Y23" s="38"/>
+      <c r="Z23" s="38"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="38"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="38"/>
+      <c r="T24" s="38"/>
+      <c r="U24" s="38"/>
+      <c r="V24" s="38"/>
+      <c r="W24" s="38"/>
+      <c r="X24" s="38"/>
+      <c r="Y24" s="38"/>
+      <c r="Z24" s="38"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="38"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
+      <c r="P25" s="38"/>
+      <c r="Q25" s="38"/>
+      <c r="R25" s="38"/>
+      <c r="S25" s="38"/>
+      <c r="T25" s="38"/>
+      <c r="U25" s="38"/>
+      <c r="V25" s="38"/>
+      <c r="W25" s="38"/>
+      <c r="X25" s="38"/>
+      <c r="Y25" s="38"/>
+      <c r="Z25" s="38"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="38"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="38"/>
+      <c r="S26" s="38"/>
+      <c r="T26" s="38"/>
+      <c r="U26" s="38"/>
+      <c r="V26" s="38"/>
+      <c r="W26" s="38"/>
+      <c r="X26" s="38"/>
+      <c r="Y26" s="38"/>
+      <c r="Z26" s="38"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="38"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="38"/>
+      <c r="P27" s="38"/>
+      <c r="Q27" s="38"/>
+      <c r="R27" s="38"/>
+      <c r="S27" s="38"/>
+      <c r="T27" s="38"/>
+      <c r="U27" s="38"/>
+      <c r="V27" s="38"/>
+      <c r="W27" s="38"/>
+      <c r="X27" s="38"/>
+      <c r="Y27" s="38"/>
+      <c r="Z27" s="38"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="38"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="38"/>
+      <c r="P28" s="38"/>
+      <c r="Q28" s="38"/>
+      <c r="R28" s="38"/>
+      <c r="S28" s="38"/>
+      <c r="T28" s="38"/>
+      <c r="U28" s="38"/>
+      <c r="V28" s="38"/>
+      <c r="W28" s="38"/>
+      <c r="X28" s="38"/>
+      <c r="Y28" s="38"/>
+      <c r="Z28" s="38"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="38"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="38"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="38"/>
+      <c r="P29" s="38"/>
+      <c r="Q29" s="38"/>
+      <c r="R29" s="38"/>
+      <c r="S29" s="38"/>
+      <c r="T29" s="38"/>
+      <c r="U29" s="38"/>
+      <c r="V29" s="38"/>
+      <c r="W29" s="38"/>
+      <c r="X29" s="38"/>
+      <c r="Y29" s="38"/>
+      <c r="Z29" s="38"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="38"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="38"/>
+      <c r="M30" s="38"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="38"/>
+      <c r="P30" s="38"/>
+      <c r="Q30" s="38"/>
+      <c r="R30" s="38"/>
+      <c r="S30" s="38"/>
+      <c r="T30" s="38"/>
+      <c r="U30" s="38"/>
+      <c r="V30" s="38"/>
+      <c r="W30" s="38"/>
+      <c r="X30" s="38"/>
+      <c r="Y30" s="38"/>
+      <c r="Z30" s="38"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="38"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38"/>
+      <c r="P31" s="38"/>
+      <c r="Q31" s="38"/>
+      <c r="R31" s="38"/>
+      <c r="S31" s="38"/>
+      <c r="T31" s="38"/>
+      <c r="U31" s="38"/>
+      <c r="V31" s="38"/>
+      <c r="W31" s="38"/>
+      <c r="X31" s="38"/>
+      <c r="Y31" s="38"/>
+      <c r="Z31" s="38"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="38"/>
+      <c r="B32" s="38"/>
+      <c r="C32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
+      <c r="J32" s="38"/>
+      <c r="K32" s="38"/>
+      <c r="L32" s="38"/>
+      <c r="M32" s="38"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="38"/>
+      <c r="P32" s="38"/>
+      <c r="Q32" s="38"/>
+      <c r="R32" s="38"/>
+      <c r="S32" s="38"/>
+      <c r="T32" s="38"/>
+      <c r="U32" s="38"/>
+      <c r="V32" s="38"/>
+      <c r="W32" s="38"/>
+      <c r="X32" s="38"/>
+      <c r="Y32" s="38"/>
+      <c r="Z32" s="38"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="38"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
+      <c r="J33" s="38"/>
+      <c r="K33" s="38"/>
+      <c r="L33" s="38"/>
+      <c r="M33" s="38"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="38"/>
+      <c r="P33" s="38"/>
+      <c r="Q33" s="38"/>
+      <c r="R33" s="38"/>
+      <c r="S33" s="38"/>
+      <c r="T33" s="38"/>
+      <c r="U33" s="38"/>
+      <c r="V33" s="38"/>
+      <c r="W33" s="38"/>
+      <c r="X33" s="38"/>
+      <c r="Y33" s="38"/>
+      <c r="Z33" s="38"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="38"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="38"/>
+      <c r="P34" s="38"/>
+      <c r="Q34" s="38"/>
+      <c r="R34" s="38"/>
+      <c r="S34" s="38"/>
+      <c r="T34" s="38"/>
+      <c r="U34" s="38"/>
+      <c r="V34" s="38"/>
+      <c r="W34" s="38"/>
+      <c r="X34" s="38"/>
+      <c r="Y34" s="38"/>
+      <c r="Z34" s="38"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="38"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="38"/>
+      <c r="P35" s="38"/>
+      <c r="Q35" s="38"/>
+      <c r="R35" s="38"/>
+      <c r="S35" s="38"/>
+      <c r="T35" s="38"/>
+      <c r="U35" s="38"/>
+      <c r="V35" s="38"/>
+      <c r="W35" s="38"/>
+      <c r="X35" s="38"/>
+      <c r="Y35" s="38"/>
+      <c r="Z35" s="38"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="38"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="38"/>
+      <c r="P36" s="38"/>
+      <c r="Q36" s="38"/>
+      <c r="R36" s="38"/>
+      <c r="S36" s="38"/>
+      <c r="T36" s="38"/>
+      <c r="U36" s="38"/>
+      <c r="V36" s="38"/>
+      <c r="W36" s="38"/>
+      <c r="X36" s="38"/>
+      <c r="Y36" s="38"/>
+      <c r="Z36" s="38"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="38"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="38"/>
+      <c r="J37" s="38"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="38"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="38"/>
+      <c r="P37" s="38"/>
+      <c r="Q37" s="38"/>
+      <c r="R37" s="38"/>
+      <c r="S37" s="38"/>
+      <c r="T37" s="38"/>
+      <c r="U37" s="38"/>
+      <c r="V37" s="38"/>
+      <c r="W37" s="38"/>
+      <c r="X37" s="38"/>
+      <c r="Y37" s="38"/>
+      <c r="Z37" s="38"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="38"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+      <c r="J38" s="38"/>
+      <c r="K38" s="38"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="38"/>
+      <c r="O38" s="38"/>
+      <c r="P38" s="38"/>
+      <c r="Q38" s="38"/>
+      <c r="R38" s="38"/>
+      <c r="S38" s="38"/>
+      <c r="T38" s="38"/>
+      <c r="U38" s="38"/>
+      <c r="V38" s="38"/>
+      <c r="W38" s="38"/>
+      <c r="X38" s="38"/>
+      <c r="Y38" s="38"/>
+      <c r="Z38" s="38"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="38"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="38"/>
+      <c r="J39" s="38"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="38"/>
+      <c r="M39" s="38"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="38"/>
+      <c r="P39" s="38"/>
+      <c r="Q39" s="38"/>
+      <c r="R39" s="38"/>
+      <c r="S39" s="38"/>
+      <c r="T39" s="38"/>
+      <c r="U39" s="38"/>
+      <c r="V39" s="38"/>
+      <c r="W39" s="38"/>
+      <c r="X39" s="38"/>
+      <c r="Y39" s="38"/>
+      <c r="Z39" s="38"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="38"/>
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
+      <c r="J40" s="38"/>
+      <c r="K40" s="38"/>
+      <c r="L40" s="38"/>
+      <c r="M40" s="38"/>
+      <c r="N40" s="38"/>
+      <c r="O40" s="38"/>
+      <c r="P40" s="38"/>
+      <c r="Q40" s="38"/>
+      <c r="R40" s="38"/>
+      <c r="S40" s="38"/>
+      <c r="T40" s="38"/>
+      <c r="U40" s="38"/>
+      <c r="V40" s="38"/>
+      <c r="W40" s="38"/>
+      <c r="X40" s="38"/>
+      <c r="Y40" s="38"/>
+      <c r="Z40" s="38"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="38"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
+      <c r="J41" s="38"/>
+      <c r="K41" s="38"/>
+      <c r="L41" s="38"/>
+      <c r="M41" s="38"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="38"/>
+      <c r="P41" s="38"/>
+      <c r="Q41" s="38"/>
+      <c r="R41" s="38"/>
+      <c r="S41" s="38"/>
+      <c r="T41" s="38"/>
+      <c r="U41" s="38"/>
+      <c r="V41" s="38"/>
+      <c r="W41" s="38"/>
+      <c r="X41" s="38"/>
+      <c r="Y41" s="38"/>
+      <c r="Z41" s="38"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="38"/>
+      <c r="B42" s="38"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="38"/>
+      <c r="J42" s="38"/>
+      <c r="K42" s="38"/>
+      <c r="L42" s="38"/>
+      <c r="M42" s="38"/>
+      <c r="N42" s="38"/>
+      <c r="O42" s="38"/>
+      <c r="P42" s="38"/>
+      <c r="Q42" s="38"/>
+      <c r="R42" s="38"/>
+      <c r="S42" s="38"/>
+      <c r="T42" s="38"/>
+      <c r="U42" s="38"/>
+      <c r="V42" s="38"/>
+      <c r="W42" s="38"/>
+      <c r="X42" s="38"/>
+      <c r="Y42" s="38"/>
+      <c r="Z42" s="38"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="38"/>
+      <c r="B43" s="38"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="38"/>
+      <c r="K43" s="38"/>
+      <c r="L43" s="38"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="38"/>
+      <c r="Q43" s="38"/>
+      <c r="R43" s="38"/>
+      <c r="S43" s="38"/>
+      <c r="T43" s="38"/>
+      <c r="U43" s="38"/>
+      <c r="V43" s="38"/>
+      <c r="W43" s="38"/>
+      <c r="X43" s="38"/>
+      <c r="Y43" s="38"/>
+      <c r="Z43" s="38"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="38"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="38"/>
+      <c r="K44" s="38"/>
+      <c r="L44" s="38"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="38"/>
+      <c r="Q44" s="38"/>
+      <c r="R44" s="38"/>
+      <c r="S44" s="38"/>
+      <c r="T44" s="38"/>
+      <c r="U44" s="38"/>
+      <c r="V44" s="38"/>
+      <c r="W44" s="38"/>
+      <c r="X44" s="38"/>
+      <c r="Y44" s="38"/>
+      <c r="Z44" s="38"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="38"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="38"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="38"/>
+      <c r="J45" s="38"/>
+      <c r="K45" s="38"/>
+      <c r="L45" s="38"/>
+      <c r="M45" s="38"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="38"/>
+      <c r="P45" s="38"/>
+      <c r="Q45" s="38"/>
+      <c r="R45" s="38"/>
+      <c r="S45" s="38"/>
+      <c r="T45" s="38"/>
+      <c r="U45" s="38"/>
+      <c r="V45" s="38"/>
+      <c r="W45" s="38"/>
+      <c r="X45" s="38"/>
+      <c r="Y45" s="38"/>
+      <c r="Z45" s="38"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="38"/>
+      <c r="B46" s="38"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="38"/>
+      <c r="K46" s="38"/>
+      <c r="L46" s="38"/>
+      <c r="M46" s="38"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="38"/>
+      <c r="Q46" s="38"/>
+      <c r="R46" s="38"/>
+      <c r="S46" s="38"/>
+      <c r="T46" s="38"/>
+      <c r="U46" s="38"/>
+      <c r="V46" s="38"/>
+      <c r="W46" s="38"/>
+      <c r="X46" s="38"/>
+      <c r="Y46" s="38"/>
+      <c r="Z46" s="38"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="38"/>
+      <c r="B47" s="38"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="38"/>
+      <c r="J47" s="38"/>
+      <c r="K47" s="38"/>
+      <c r="L47" s="38"/>
+      <c r="M47" s="38"/>
+      <c r="N47" s="38"/>
+      <c r="O47" s="38"/>
+      <c r="P47" s="38"/>
+      <c r="Q47" s="38"/>
+      <c r="R47" s="38"/>
+      <c r="S47" s="38"/>
+      <c r="T47" s="38"/>
+      <c r="U47" s="38"/>
+      <c r="V47" s="38"/>
+      <c r="W47" s="38"/>
+      <c r="X47" s="38"/>
+      <c r="Y47" s="38"/>
+      <c r="Z47" s="38"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="38"/>
+      <c r="B48" s="38"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="38"/>
+      <c r="E48" s="38"/>
+      <c r="F48" s="38"/>
+      <c r="G48" s="38"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="38"/>
+      <c r="J48" s="38"/>
+      <c r="K48" s="38"/>
+      <c r="L48" s="38"/>
+      <c r="M48" s="38"/>
+      <c r="N48" s="38"/>
+      <c r="O48" s="38"/>
+      <c r="P48" s="38"/>
+      <c r="Q48" s="38"/>
+      <c r="R48" s="38"/>
+      <c r="S48" s="38"/>
+      <c r="T48" s="38"/>
+      <c r="U48" s="38"/>
+      <c r="V48" s="38"/>
+      <c r="W48" s="38"/>
+      <c r="X48" s="38"/>
+      <c r="Y48" s="38"/>
+      <c r="Z48" s="38"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="38"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="38"/>
+      <c r="J49" s="38"/>
+      <c r="K49" s="38"/>
+      <c r="L49" s="38"/>
+      <c r="M49" s="38"/>
+      <c r="N49" s="38"/>
+      <c r="O49" s="38"/>
+      <c r="P49" s="38"/>
+      <c r="Q49" s="38"/>
+      <c r="R49" s="38"/>
+      <c r="S49" s="38"/>
+      <c r="T49" s="38"/>
+      <c r="U49" s="38"/>
+      <c r="V49" s="38"/>
+      <c r="W49" s="38"/>
+      <c r="X49" s="38"/>
+      <c r="Y49" s="38"/>
+      <c r="Z49" s="38"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="38"/>
+      <c r="B50" s="38"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="38"/>
+      <c r="J50" s="38"/>
+      <c r="K50" s="38"/>
+      <c r="L50" s="38"/>
+      <c r="M50" s="38"/>
+      <c r="N50" s="38"/>
+      <c r="O50" s="38"/>
+      <c r="P50" s="38"/>
+      <c r="Q50" s="38"/>
+      <c r="R50" s="38"/>
+      <c r="S50" s="38"/>
+      <c r="T50" s="38"/>
+      <c r="U50" s="38"/>
+      <c r="V50" s="38"/>
+      <c r="W50" s="38"/>
+      <c r="X50" s="38"/>
+      <c r="Y50" s="38"/>
+      <c r="Z50" s="38"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="38"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="38"/>
+      <c r="F51" s="38"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="38"/>
+      <c r="I51" s="38"/>
+      <c r="J51" s="38"/>
+      <c r="K51" s="38"/>
+      <c r="L51" s="38"/>
+      <c r="M51" s="38"/>
+      <c r="N51" s="38"/>
+      <c r="O51" s="38"/>
+      <c r="P51" s="38"/>
+      <c r="Q51" s="38"/>
+      <c r="R51" s="38"/>
+      <c r="S51" s="38"/>
+      <c r="T51" s="38"/>
+      <c r="U51" s="38"/>
+      <c r="V51" s="38"/>
+      <c r="W51" s="38"/>
+      <c r="X51" s="38"/>
+      <c r="Y51" s="38"/>
+      <c r="Z51" s="38"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="38"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="38"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="38"/>
+      <c r="K52" s="38"/>
+      <c r="L52" s="38"/>
+      <c r="M52" s="38"/>
+      <c r="N52" s="38"/>
+      <c r="O52" s="38"/>
+      <c r="P52" s="38"/>
+      <c r="Q52" s="38"/>
+      <c r="R52" s="38"/>
+      <c r="S52" s="38"/>
+      <c r="T52" s="38"/>
+      <c r="U52" s="38"/>
+      <c r="V52" s="38"/>
+      <c r="W52" s="38"/>
+      <c r="X52" s="38"/>
+      <c r="Y52" s="38"/>
+      <c r="Z52" s="38"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="38"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="38"/>
+      <c r="J53" s="38"/>
+      <c r="K53" s="38"/>
+      <c r="L53" s="38"/>
+      <c r="M53" s="38"/>
+      <c r="N53" s="38"/>
+      <c r="O53" s="38"/>
+      <c r="P53" s="38"/>
+      <c r="Q53" s="38"/>
+      <c r="R53" s="38"/>
+      <c r="S53" s="38"/>
+      <c r="T53" s="38"/>
+      <c r="U53" s="38"/>
+      <c r="V53" s="38"/>
+      <c r="W53" s="38"/>
+      <c r="X53" s="38"/>
+      <c r="Y53" s="38"/>
+      <c r="Z53" s="38"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="38"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="38"/>
+      <c r="J54" s="38"/>
+      <c r="K54" s="38"/>
+      <c r="L54" s="38"/>
+      <c r="M54" s="38"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="38"/>
+      <c r="P54" s="38"/>
+      <c r="Q54" s="38"/>
+      <c r="R54" s="38"/>
+      <c r="S54" s="38"/>
+      <c r="T54" s="38"/>
+      <c r="U54" s="38"/>
+      <c r="V54" s="38"/>
+      <c r="W54" s="38"/>
+      <c r="X54" s="38"/>
+      <c r="Y54" s="38"/>
+      <c r="Z54" s="38"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="38"/>
+      <c r="B55" s="38"/>
+      <c r="C55" s="38"/>
+      <c r="D55" s="38"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="38"/>
+      <c r="G55" s="38"/>
+      <c r="H55" s="38"/>
+      <c r="I55" s="38"/>
+      <c r="J55" s="38"/>
+      <c r="K55" s="38"/>
+      <c r="L55" s="38"/>
+      <c r="M55" s="38"/>
+      <c r="N55" s="38"/>
+      <c r="O55" s="38"/>
+      <c r="P55" s="38"/>
+      <c r="Q55" s="38"/>
+      <c r="R55" s="38"/>
+      <c r="S55" s="38"/>
+      <c r="T55" s="38"/>
+      <c r="U55" s="38"/>
+      <c r="V55" s="38"/>
+      <c r="W55" s="38"/>
+      <c r="X55" s="38"/>
+      <c r="Y55" s="38"/>
+      <c r="Z55" s="38"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="38"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="38"/>
+      <c r="I56" s="38"/>
+      <c r="J56" s="38"/>
+      <c r="K56" s="38"/>
+      <c r="L56" s="38"/>
+      <c r="M56" s="38"/>
+      <c r="N56" s="38"/>
+      <c r="O56" s="38"/>
+      <c r="P56" s="38"/>
+      <c r="Q56" s="38"/>
+      <c r="R56" s="38"/>
+      <c r="S56" s="38"/>
+      <c r="T56" s="38"/>
+      <c r="U56" s="38"/>
+      <c r="V56" s="38"/>
+      <c r="W56" s="38"/>
+      <c r="X56" s="38"/>
+      <c r="Y56" s="38"/>
+      <c r="Z56" s="38"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="38"/>
+      <c r="B57" s="38"/>
+      <c r="C57" s="38"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="38"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="38"/>
+      <c r="I57" s="38"/>
+      <c r="J57" s="38"/>
+      <c r="K57" s="38"/>
+      <c r="L57" s="38"/>
+      <c r="M57" s="38"/>
+      <c r="N57" s="38"/>
+      <c r="O57" s="38"/>
+      <c r="P57" s="38"/>
+      <c r="Q57" s="38"/>
+      <c r="R57" s="38"/>
+      <c r="S57" s="38"/>
+      <c r="T57" s="38"/>
+      <c r="U57" s="38"/>
+      <c r="V57" s="38"/>
+      <c r="W57" s="38"/>
+      <c r="X57" s="38"/>
+      <c r="Y57" s="38"/>
+      <c r="Z57" s="38"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="38"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="38"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="38"/>
+      <c r="I58" s="38"/>
+      <c r="J58" s="38"/>
+      <c r="K58" s="38"/>
+      <c r="L58" s="38"/>
+      <c r="M58" s="38"/>
+      <c r="N58" s="38"/>
+      <c r="O58" s="38"/>
+      <c r="P58" s="38"/>
+      <c r="Q58" s="38"/>
+      <c r="R58" s="38"/>
+      <c r="S58" s="38"/>
+      <c r="T58" s="38"/>
+      <c r="U58" s="38"/>
+      <c r="V58" s="38"/>
+      <c r="W58" s="38"/>
+      <c r="X58" s="38"/>
+      <c r="Y58" s="38"/>
+      <c r="Z58" s="38"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="38"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="38"/>
+      <c r="E59" s="38"/>
+      <c r="F59" s="38"/>
+      <c r="G59" s="38"/>
+      <c r="H59" s="38"/>
+      <c r="I59" s="38"/>
+      <c r="J59" s="38"/>
+      <c r="K59" s="38"/>
+      <c r="L59" s="38"/>
+      <c r="M59" s="38"/>
+      <c r="N59" s="38"/>
+      <c r="O59" s="38"/>
+      <c r="P59" s="38"/>
+      <c r="Q59" s="38"/>
+      <c r="R59" s="38"/>
+      <c r="S59" s="38"/>
+      <c r="T59" s="38"/>
+      <c r="U59" s="38"/>
+      <c r="V59" s="38"/>
+      <c r="W59" s="38"/>
+      <c r="X59" s="38"/>
+      <c r="Y59" s="38"/>
+      <c r="Z59" s="38"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="38"/>
+      <c r="B60" s="38"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="38"/>
+      <c r="F60" s="38"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="38"/>
+      <c r="J60" s="38"/>
+      <c r="K60" s="38"/>
+      <c r="L60" s="38"/>
+      <c r="M60" s="38"/>
+      <c r="N60" s="38"/>
+      <c r="O60" s="38"/>
+      <c r="P60" s="38"/>
+      <c r="Q60" s="38"/>
+      <c r="R60" s="38"/>
+      <c r="S60" s="38"/>
+      <c r="T60" s="38"/>
+      <c r="U60" s="38"/>
+      <c r="V60" s="38"/>
+      <c r="W60" s="38"/>
+      <c r="X60" s="38"/>
+      <c r="Y60" s="38"/>
+      <c r="Z60" s="38"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="38"/>
+      <c r="B61" s="38"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="38"/>
+      <c r="G61" s="38"/>
+      <c r="H61" s="38"/>
+      <c r="I61" s="38"/>
+      <c r="J61" s="38"/>
+      <c r="K61" s="38"/>
+      <c r="L61" s="38"/>
+      <c r="M61" s="38"/>
+      <c r="N61" s="38"/>
+      <c r="O61" s="38"/>
+      <c r="P61" s="38"/>
+      <c r="Q61" s="38"/>
+      <c r="R61" s="38"/>
+      <c r="S61" s="38"/>
+      <c r="T61" s="38"/>
+      <c r="U61" s="38"/>
+      <c r="V61" s="38"/>
+      <c r="W61" s="38"/>
+      <c r="X61" s="38"/>
+      <c r="Y61" s="38"/>
+      <c r="Z61" s="38"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="38"/>
+      <c r="B62" s="38"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="38"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
+      <c r="K62" s="38"/>
+      <c r="L62" s="38"/>
+      <c r="M62" s="38"/>
+      <c r="N62" s="38"/>
+      <c r="O62" s="38"/>
+      <c r="P62" s="38"/>
+      <c r="Q62" s="38"/>
+      <c r="R62" s="38"/>
+      <c r="S62" s="38"/>
+      <c r="T62" s="38"/>
+      <c r="U62" s="38"/>
+      <c r="V62" s="38"/>
+      <c r="W62" s="38"/>
+      <c r="X62" s="38"/>
+      <c r="Y62" s="38"/>
+      <c r="Z62" s="38"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="38"/>
+      <c r="B63" s="38"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="38"/>
+      <c r="E63" s="38"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="38"/>
+      <c r="K63" s="38"/>
+      <c r="L63" s="38"/>
+      <c r="M63" s="38"/>
+      <c r="N63" s="38"/>
+      <c r="O63" s="38"/>
+      <c r="P63" s="38"/>
+      <c r="Q63" s="38"/>
+      <c r="R63" s="38"/>
+      <c r="S63" s="38"/>
+      <c r="T63" s="38"/>
+      <c r="U63" s="38"/>
+      <c r="V63" s="38"/>
+      <c r="W63" s="38"/>
+      <c r="X63" s="38"/>
+      <c r="Y63" s="38"/>
+      <c r="Z63" s="38"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="38"/>
+      <c r="B64" s="38"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="38"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="38"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="38"/>
+      <c r="J64" s="38"/>
+      <c r="K64" s="38"/>
+      <c r="L64" s="38"/>
+      <c r="M64" s="38"/>
+      <c r="N64" s="38"/>
+      <c r="O64" s="38"/>
+      <c r="P64" s="38"/>
+      <c r="Q64" s="38"/>
+      <c r="R64" s="38"/>
+      <c r="S64" s="38"/>
+      <c r="T64" s="38"/>
+      <c r="U64" s="38"/>
+      <c r="V64" s="38"/>
+      <c r="W64" s="38"/>
+      <c r="X64" s="38"/>
+      <c r="Y64" s="38"/>
+      <c r="Z64" s="38"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="38"/>
+      <c r="B65" s="38"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="38"/>
+      <c r="F65" s="38"/>
+      <c r="G65" s="38"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="38"/>
+      <c r="J65" s="38"/>
+      <c r="K65" s="38"/>
+      <c r="L65" s="38"/>
+      <c r="M65" s="38"/>
+      <c r="N65" s="38"/>
+      <c r="O65" s="38"/>
+      <c r="P65" s="38"/>
+      <c r="Q65" s="38"/>
+      <c r="R65" s="38"/>
+      <c r="S65" s="38"/>
+      <c r="T65" s="38"/>
+      <c r="U65" s="38"/>
+      <c r="V65" s="38"/>
+      <c r="W65" s="38"/>
+      <c r="X65" s="38"/>
+      <c r="Y65" s="38"/>
+      <c r="Z65" s="38"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="38"/>
+      <c r="B66" s="38"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="38"/>
+      <c r="F66" s="38"/>
+      <c r="G66" s="38"/>
+      <c r="H66" s="38"/>
+      <c r="I66" s="38"/>
+      <c r="J66" s="38"/>
+      <c r="K66" s="38"/>
+      <c r="L66" s="38"/>
+      <c r="M66" s="38"/>
+      <c r="N66" s="38"/>
+      <c r="O66" s="38"/>
+      <c r="P66" s="38"/>
+      <c r="Q66" s="38"/>
+      <c r="R66" s="38"/>
+      <c r="S66" s="38"/>
+      <c r="T66" s="38"/>
+      <c r="U66" s="38"/>
+      <c r="V66" s="38"/>
+      <c r="W66" s="38"/>
+      <c r="X66" s="38"/>
+      <c r="Y66" s="38"/>
+      <c r="Z66" s="38"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="38"/>
+      <c r="B67" s="38"/>
+      <c r="C67" s="38"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="38"/>
+      <c r="F67" s="38"/>
+      <c r="G67" s="38"/>
+      <c r="H67" s="38"/>
+      <c r="I67" s="38"/>
+      <c r="J67" s="38"/>
+      <c r="K67" s="38"/>
+      <c r="L67" s="38"/>
+      <c r="M67" s="38"/>
+      <c r="N67" s="38"/>
+      <c r="O67" s="38"/>
+      <c r="P67" s="38"/>
+      <c r="Q67" s="38"/>
+      <c r="R67" s="38"/>
+      <c r="S67" s="38"/>
+      <c r="T67" s="38"/>
+      <c r="U67" s="38"/>
+      <c r="V67" s="38"/>
+      <c r="W67" s="38"/>
+      <c r="X67" s="38"/>
+      <c r="Y67" s="38"/>
+      <c r="Z67" s="38"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="38"/>
+      <c r="B68" s="38"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="38"/>
+      <c r="G68" s="38"/>
+      <c r="H68" s="38"/>
+      <c r="I68" s="38"/>
+      <c r="J68" s="38"/>
+      <c r="K68" s="38"/>
+      <c r="L68" s="38"/>
+      <c r="M68" s="38"/>
+      <c r="N68" s="38"/>
+      <c r="O68" s="38"/>
+      <c r="P68" s="38"/>
+      <c r="Q68" s="38"/>
+      <c r="R68" s="38"/>
+      <c r="S68" s="38"/>
+      <c r="T68" s="38"/>
+      <c r="U68" s="38"/>
+      <c r="V68" s="38"/>
+      <c r="W68" s="38"/>
+      <c r="X68" s="38"/>
+      <c r="Y68" s="38"/>
+      <c r="Z68" s="38"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="38"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="38"/>
+      <c r="G69" s="38"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="38"/>
+      <c r="J69" s="38"/>
+      <c r="K69" s="38"/>
+      <c r="L69" s="38"/>
+      <c r="M69" s="38"/>
+      <c r="N69" s="38"/>
+      <c r="O69" s="38"/>
+      <c r="P69" s="38"/>
+      <c r="Q69" s="38"/>
+      <c r="R69" s="38"/>
+      <c r="S69" s="38"/>
+      <c r="T69" s="38"/>
+      <c r="U69" s="38"/>
+      <c r="V69" s="38"/>
+      <c r="W69" s="38"/>
+      <c r="X69" s="38"/>
+      <c r="Y69" s="38"/>
+      <c r="Z69" s="38"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="38"/>
+      <c r="B70" s="38"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="38"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
+      <c r="J70" s="38"/>
+      <c r="K70" s="38"/>
+      <c r="L70" s="38"/>
+      <c r="M70" s="38"/>
+      <c r="N70" s="38"/>
+      <c r="O70" s="38"/>
+      <c r="P70" s="38"/>
+      <c r="Q70" s="38"/>
+      <c r="R70" s="38"/>
+      <c r="S70" s="38"/>
+      <c r="T70" s="38"/>
+      <c r="U70" s="38"/>
+      <c r="V70" s="38"/>
+      <c r="W70" s="38"/>
+      <c r="X70" s="38"/>
+      <c r="Y70" s="38"/>
+      <c r="Z70" s="38"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="38"/>
+      <c r="B71" s="38"/>
+      <c r="C71" s="38"/>
+      <c r="D71" s="38"/>
+      <c r="E71" s="38"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
+      <c r="J71" s="38"/>
+      <c r="K71" s="38"/>
+      <c r="L71" s="38"/>
+      <c r="M71" s="38"/>
+      <c r="N71" s="38"/>
+      <c r="O71" s="38"/>
+      <c r="P71" s="38"/>
+      <c r="Q71" s="38"/>
+      <c r="R71" s="38"/>
+      <c r="S71" s="38"/>
+      <c r="T71" s="38"/>
+      <c r="U71" s="38"/>
+      <c r="V71" s="38"/>
+      <c r="W71" s="38"/>
+      <c r="X71" s="38"/>
+      <c r="Y71" s="38"/>
+      <c r="Z71" s="38"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="38"/>
+      <c r="B72" s="38"/>
+      <c r="C72" s="38"/>
+      <c r="D72" s="38"/>
+      <c r="E72" s="38"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="38"/>
+      <c r="H72" s="38"/>
+      <c r="I72" s="38"/>
+      <c r="J72" s="38"/>
+      <c r="K72" s="38"/>
+      <c r="L72" s="38"/>
+      <c r="M72" s="38"/>
+      <c r="N72" s="38"/>
+      <c r="O72" s="38"/>
+      <c r="P72" s="38"/>
+      <c r="Q72" s="38"/>
+      <c r="R72" s="38"/>
+      <c r="S72" s="38"/>
+      <c r="T72" s="38"/>
+      <c r="U72" s="38"/>
+      <c r="V72" s="38"/>
+      <c r="W72" s="38"/>
+      <c r="X72" s="38"/>
+      <c r="Y72" s="38"/>
+      <c r="Z72" s="38"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="38"/>
+      <c r="B73" s="38"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="38"/>
+      <c r="F73" s="38"/>
+      <c r="G73" s="38"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="38"/>
+      <c r="J73" s="38"/>
+      <c r="K73" s="38"/>
+      <c r="L73" s="38"/>
+      <c r="M73" s="38"/>
+      <c r="N73" s="38"/>
+      <c r="O73" s="38"/>
+      <c r="P73" s="38"/>
+      <c r="Q73" s="38"/>
+      <c r="R73" s="38"/>
+      <c r="S73" s="38"/>
+      <c r="T73" s="38"/>
+      <c r="U73" s="38"/>
+      <c r="V73" s="38"/>
+      <c r="W73" s="38"/>
+      <c r="X73" s="38"/>
+      <c r="Y73" s="38"/>
+      <c r="Z73" s="38"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="38"/>
+      <c r="B74" s="38"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="38"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="38"/>
+      <c r="G74" s="38"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="38"/>
+      <c r="J74" s="38"/>
+      <c r="K74" s="38"/>
+      <c r="L74" s="38"/>
+      <c r="M74" s="38"/>
+      <c r="N74" s="38"/>
+      <c r="O74" s="38"/>
+      <c r="P74" s="38"/>
+      <c r="Q74" s="38"/>
+      <c r="R74" s="38"/>
+      <c r="S74" s="38"/>
+      <c r="T74" s="38"/>
+      <c r="U74" s="38"/>
+      <c r="V74" s="38"/>
+      <c r="W74" s="38"/>
+      <c r="X74" s="38"/>
+      <c r="Y74" s="38"/>
+      <c r="Z74" s="38"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="38"/>
+      <c r="B75" s="38"/>
+      <c r="C75" s="38"/>
+      <c r="D75" s="38"/>
+      <c r="E75" s="38"/>
+      <c r="F75" s="38"/>
+      <c r="G75" s="38"/>
+      <c r="H75" s="38"/>
+      <c r="I75" s="38"/>
+      <c r="J75" s="38"/>
+      <c r="K75" s="38"/>
+      <c r="L75" s="38"/>
+      <c r="M75" s="38"/>
+      <c r="N75" s="38"/>
+      <c r="O75" s="38"/>
+      <c r="P75" s="38"/>
+      <c r="Q75" s="38"/>
+      <c r="R75" s="38"/>
+      <c r="S75" s="38"/>
+      <c r="T75" s="38"/>
+      <c r="U75" s="38"/>
+      <c r="V75" s="38"/>
+      <c r="W75" s="38"/>
+      <c r="X75" s="38"/>
+      <c r="Y75" s="38"/>
+      <c r="Z75" s="38"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="38"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="38"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="38"/>
+      <c r="G76" s="38"/>
+      <c r="H76" s="38"/>
+      <c r="I76" s="38"/>
+      <c r="J76" s="38"/>
+      <c r="K76" s="38"/>
+      <c r="L76" s="38"/>
+      <c r="M76" s="38"/>
+      <c r="N76" s="38"/>
+      <c r="O76" s="38"/>
+      <c r="P76" s="38"/>
+      <c r="Q76" s="38"/>
+      <c r="R76" s="38"/>
+      <c r="S76" s="38"/>
+      <c r="T76" s="38"/>
+      <c r="U76" s="38"/>
+      <c r="V76" s="38"/>
+      <c r="W76" s="38"/>
+      <c r="X76" s="38"/>
+      <c r="Y76" s="38"/>
+      <c r="Z76" s="38"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="38"/>
+      <c r="B77" s="38"/>
+      <c r="C77" s="38"/>
+      <c r="D77" s="38"/>
+      <c r="E77" s="38"/>
+      <c r="F77" s="38"/>
+      <c r="G77" s="38"/>
+      <c r="H77" s="38"/>
+      <c r="I77" s="38"/>
+      <c r="J77" s="38"/>
+      <c r="K77" s="38"/>
+      <c r="L77" s="38"/>
+      <c r="M77" s="38"/>
+      <c r="N77" s="38"/>
+      <c r="O77" s="38"/>
+      <c r="P77" s="38"/>
+      <c r="Q77" s="38"/>
+      <c r="R77" s="38"/>
+      <c r="S77" s="38"/>
+      <c r="T77" s="38"/>
+      <c r="U77" s="38"/>
+      <c r="V77" s="38"/>
+      <c r="W77" s="38"/>
+      <c r="X77" s="38"/>
+      <c r="Y77" s="38"/>
+      <c r="Z77" s="38"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="38"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="38"/>
+      <c r="H78" s="38"/>
+      <c r="I78" s="38"/>
+      <c r="J78" s="38"/>
+      <c r="K78" s="38"/>
+      <c r="L78" s="38"/>
+      <c r="M78" s="38"/>
+      <c r="N78" s="38"/>
+      <c r="O78" s="38"/>
+      <c r="P78" s="38"/>
+      <c r="Q78" s="38"/>
+      <c r="R78" s="38"/>
+      <c r="S78" s="38"/>
+      <c r="T78" s="38"/>
+      <c r="U78" s="38"/>
+      <c r="V78" s="38"/>
+      <c r="W78" s="38"/>
+      <c r="X78" s="38"/>
+      <c r="Y78" s="38"/>
+      <c r="Z78" s="38"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="38"/>
+      <c r="B79" s="38"/>
+      <c r="C79" s="38"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38"/>
+      <c r="G79" s="38"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="38"/>
+      <c r="J79" s="38"/>
+      <c r="K79" s="38"/>
+      <c r="L79" s="38"/>
+      <c r="M79" s="38"/>
+      <c r="N79" s="38"/>
+      <c r="O79" s="38"/>
+      <c r="P79" s="38"/>
+      <c r="Q79" s="38"/>
+      <c r="R79" s="38"/>
+      <c r="S79" s="38"/>
+      <c r="T79" s="38"/>
+      <c r="U79" s="38"/>
+      <c r="V79" s="38"/>
+      <c r="W79" s="38"/>
+      <c r="X79" s="38"/>
+      <c r="Y79" s="38"/>
+      <c r="Z79" s="38"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="38"/>
+      <c r="B80" s="38"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="38"/>
+      <c r="F80" s="38"/>
+      <c r="G80" s="38"/>
+      <c r="H80" s="38"/>
+      <c r="I80" s="38"/>
+      <c r="J80" s="38"/>
+      <c r="K80" s="38"/>
+      <c r="L80" s="38"/>
+      <c r="M80" s="38"/>
+      <c r="N80" s="38"/>
+      <c r="O80" s="38"/>
+      <c r="P80" s="38"/>
+      <c r="Q80" s="38"/>
+      <c r="R80" s="38"/>
+      <c r="S80" s="38"/>
+      <c r="T80" s="38"/>
+      <c r="U80" s="38"/>
+      <c r="V80" s="38"/>
+      <c r="W80" s="38"/>
+      <c r="X80" s="38"/>
+      <c r="Y80" s="38"/>
+      <c r="Z80" s="38"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="38"/>
+      <c r="B81" s="38"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="38"/>
+      <c r="G81" s="38"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="38"/>
+      <c r="J81" s="38"/>
+      <c r="K81" s="38"/>
+      <c r="L81" s="38"/>
+      <c r="M81" s="38"/>
+      <c r="N81" s="38"/>
+      <c r="O81" s="38"/>
+      <c r="P81" s="38"/>
+      <c r="Q81" s="38"/>
+      <c r="R81" s="38"/>
+      <c r="S81" s="38"/>
+      <c r="T81" s="38"/>
+      <c r="U81" s="38"/>
+      <c r="V81" s="38"/>
+      <c r="W81" s="38"/>
+      <c r="X81" s="38"/>
+      <c r="Y81" s="38"/>
+      <c r="Z81" s="38"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="38"/>
+      <c r="B82" s="38"/>
+      <c r="C82" s="38"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="38"/>
+      <c r="F82" s="38"/>
+      <c r="G82" s="38"/>
+      <c r="H82" s="38"/>
+      <c r="I82" s="38"/>
+      <c r="J82" s="38"/>
+      <c r="K82" s="38"/>
+      <c r="L82" s="38"/>
+      <c r="M82" s="38"/>
+      <c r="N82" s="38"/>
+      <c r="O82" s="38"/>
+      <c r="P82" s="38"/>
+      <c r="Q82" s="38"/>
+      <c r="R82" s="38"/>
+      <c r="S82" s="38"/>
+      <c r="T82" s="38"/>
+      <c r="U82" s="38"/>
+      <c r="V82" s="38"/>
+      <c r="W82" s="38"/>
+      <c r="X82" s="38"/>
+      <c r="Y82" s="38"/>
+      <c r="Z82" s="38"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="38"/>
+      <c r="B83" s="38"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="38"/>
+      <c r="F83" s="38"/>
+      <c r="G83" s="38"/>
+      <c r="H83" s="38"/>
+      <c r="I83" s="38"/>
+      <c r="J83" s="38"/>
+      <c r="K83" s="38"/>
+      <c r="L83" s="38"/>
+      <c r="M83" s="38"/>
+      <c r="N83" s="38"/>
+      <c r="O83" s="38"/>
+      <c r="P83" s="38"/>
+      <c r="Q83" s="38"/>
+      <c r="R83" s="38"/>
+      <c r="S83" s="38"/>
+      <c r="T83" s="38"/>
+      <c r="U83" s="38"/>
+      <c r="V83" s="38"/>
+      <c r="W83" s="38"/>
+      <c r="X83" s="38"/>
+      <c r="Y83" s="38"/>
+      <c r="Z83" s="38"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="38"/>
+      <c r="B84" s="38"/>
+      <c r="C84" s="38"/>
+      <c r="D84" s="38"/>
+      <c r="E84" s="38"/>
+      <c r="F84" s="38"/>
+      <c r="G84" s="38"/>
+      <c r="H84" s="38"/>
+      <c r="I84" s="38"/>
+      <c r="J84" s="38"/>
+      <c r="K84" s="38"/>
+      <c r="L84" s="38"/>
+      <c r="M84" s="38"/>
+      <c r="N84" s="38"/>
+      <c r="O84" s="38"/>
+      <c r="P84" s="38"/>
+      <c r="Q84" s="38"/>
+      <c r="R84" s="38"/>
+      <c r="S84" s="38"/>
+      <c r="T84" s="38"/>
+      <c r="U84" s="38"/>
+      <c r="V84" s="38"/>
+      <c r="W84" s="38"/>
+      <c r="X84" s="38"/>
+      <c r="Y84" s="38"/>
+      <c r="Z84" s="38"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="38"/>
+      <c r="B85" s="38"/>
+      <c r="C85" s="38"/>
+      <c r="D85" s="38"/>
+      <c r="E85" s="38"/>
+      <c r="F85" s="38"/>
+      <c r="G85" s="38"/>
+      <c r="H85" s="38"/>
+      <c r="I85" s="38"/>
+      <c r="J85" s="38"/>
+      <c r="K85" s="38"/>
+      <c r="L85" s="38"/>
+      <c r="M85" s="38"/>
+      <c r="N85" s="38"/>
+      <c r="O85" s="38"/>
+      <c r="P85" s="38"/>
+      <c r="Q85" s="38"/>
+      <c r="R85" s="38"/>
+      <c r="S85" s="38"/>
+      <c r="T85" s="38"/>
+      <c r="U85" s="38"/>
+      <c r="V85" s="38"/>
+      <c r="W85" s="38"/>
+      <c r="X85" s="38"/>
+      <c r="Y85" s="38"/>
+      <c r="Z85" s="38"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="38"/>
+      <c r="B86" s="38"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="38"/>
+      <c r="F86" s="38"/>
+      <c r="G86" s="38"/>
+      <c r="H86" s="38"/>
+      <c r="I86" s="38"/>
+      <c r="J86" s="38"/>
+      <c r="K86" s="38"/>
+      <c r="L86" s="38"/>
+      <c r="M86" s="38"/>
+      <c r="N86" s="38"/>
+      <c r="O86" s="38"/>
+      <c r="P86" s="38"/>
+      <c r="Q86" s="38"/>
+      <c r="R86" s="38"/>
+      <c r="S86" s="38"/>
+      <c r="T86" s="38"/>
+      <c r="U86" s="38"/>
+      <c r="V86" s="38"/>
+      <c r="W86" s="38"/>
+      <c r="X86" s="38"/>
+      <c r="Y86" s="38"/>
+      <c r="Z86" s="38"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="38"/>
+      <c r="B87" s="38"/>
+      <c r="C87" s="38"/>
+      <c r="D87" s="38"/>
+      <c r="E87" s="38"/>
+      <c r="F87" s="38"/>
+      <c r="G87" s="38"/>
+      <c r="H87" s="38"/>
+      <c r="I87" s="38"/>
+      <c r="J87" s="38"/>
+      <c r="K87" s="38"/>
+      <c r="L87" s="38"/>
+      <c r="M87" s="38"/>
+      <c r="N87" s="38"/>
+      <c r="O87" s="38"/>
+      <c r="P87" s="38"/>
+      <c r="Q87" s="38"/>
+      <c r="R87" s="38"/>
+      <c r="S87" s="38"/>
+      <c r="T87" s="38"/>
+      <c r="U87" s="38"/>
+      <c r="V87" s="38"/>
+      <c r="W87" s="38"/>
+      <c r="X87" s="38"/>
+      <c r="Y87" s="38"/>
+      <c r="Z87" s="38"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="38"/>
+      <c r="B88" s="38"/>
+      <c r="C88" s="38"/>
+      <c r="D88" s="38"/>
+      <c r="E88" s="38"/>
+      <c r="F88" s="38"/>
+      <c r="G88" s="38"/>
+      <c r="H88" s="38"/>
+      <c r="I88" s="38"/>
+      <c r="J88" s="38"/>
+      <c r="K88" s="38"/>
+      <c r="L88" s="38"/>
+      <c r="M88" s="38"/>
+      <c r="N88" s="38"/>
+      <c r="O88" s="38"/>
+      <c r="P88" s="38"/>
+      <c r="Q88" s="38"/>
+      <c r="R88" s="38"/>
+      <c r="S88" s="38"/>
+      <c r="T88" s="38"/>
+      <c r="U88" s="38"/>
+      <c r="V88" s="38"/>
+      <c r="W88" s="38"/>
+      <c r="X88" s="38"/>
+      <c r="Y88" s="38"/>
+      <c r="Z88" s="38"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="38"/>
+      <c r="B89" s="38"/>
+      <c r="C89" s="38"/>
+      <c r="D89" s="38"/>
+      <c r="E89" s="38"/>
+      <c r="F89" s="38"/>
+      <c r="G89" s="38"/>
+      <c r="H89" s="38"/>
+      <c r="I89" s="38"/>
+      <c r="J89" s="38"/>
+      <c r="K89" s="38"/>
+      <c r="L89" s="38"/>
+      <c r="M89" s="38"/>
+      <c r="N89" s="38"/>
+      <c r="O89" s="38"/>
+      <c r="P89" s="38"/>
+      <c r="Q89" s="38"/>
+      <c r="R89" s="38"/>
+      <c r="S89" s="38"/>
+      <c r="T89" s="38"/>
+      <c r="U89" s="38"/>
+      <c r="V89" s="38"/>
+      <c r="W89" s="38"/>
+      <c r="X89" s="38"/>
+      <c r="Y89" s="38"/>
+      <c r="Z89" s="38"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="38"/>
+      <c r="B90" s="38"/>
+      <c r="C90" s="38"/>
+      <c r="D90" s="38"/>
+      <c r="E90" s="38"/>
+      <c r="F90" s="38"/>
+      <c r="G90" s="38"/>
+      <c r="H90" s="38"/>
+      <c r="I90" s="38"/>
+      <c r="J90" s="38"/>
+      <c r="K90" s="38"/>
+      <c r="L90" s="38"/>
+      <c r="M90" s="38"/>
+      <c r="N90" s="38"/>
+      <c r="O90" s="38"/>
+      <c r="P90" s="38"/>
+      <c r="Q90" s="38"/>
+      <c r="R90" s="38"/>
+      <c r="S90" s="38"/>
+      <c r="T90" s="38"/>
+      <c r="U90" s="38"/>
+      <c r="V90" s="38"/>
+      <c r="W90" s="38"/>
+      <c r="X90" s="38"/>
+      <c r="Y90" s="38"/>
+      <c r="Z90" s="38"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="38"/>
+      <c r="B91" s="38"/>
+      <c r="C91" s="38"/>
+      <c r="D91" s="38"/>
+      <c r="E91" s="38"/>
+      <c r="F91" s="38"/>
+      <c r="G91" s="38"/>
+      <c r="H91" s="38"/>
+      <c r="I91" s="38"/>
+      <c r="J91" s="38"/>
+      <c r="K91" s="38"/>
+      <c r="L91" s="38"/>
+      <c r="M91" s="38"/>
+      <c r="N91" s="38"/>
+      <c r="O91" s="38"/>
+      <c r="P91" s="38"/>
+      <c r="Q91" s="38"/>
+      <c r="R91" s="38"/>
+      <c r="S91" s="38"/>
+      <c r="T91" s="38"/>
+      <c r="U91" s="38"/>
+      <c r="V91" s="38"/>
+      <c r="W91" s="38"/>
+      <c r="X91" s="38"/>
+      <c r="Y91" s="38"/>
+      <c r="Z91" s="38"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="38"/>
+      <c r="B92" s="38"/>
+      <c r="C92" s="38"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="38"/>
+      <c r="F92" s="38"/>
+      <c r="G92" s="38"/>
+      <c r="H92" s="38"/>
+      <c r="I92" s="38"/>
+      <c r="J92" s="38"/>
+      <c r="K92" s="38"/>
+      <c r="L92" s="38"/>
+      <c r="M92" s="38"/>
+      <c r="N92" s="38"/>
+      <c r="O92" s="38"/>
+      <c r="P92" s="38"/>
+      <c r="Q92" s="38"/>
+      <c r="R92" s="38"/>
+      <c r="S92" s="38"/>
+      <c r="T92" s="38"/>
+      <c r="U92" s="38"/>
+      <c r="V92" s="38"/>
+      <c r="W92" s="38"/>
+      <c r="X92" s="38"/>
+      <c r="Y92" s="38"/>
+      <c r="Z92" s="38"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="38"/>
+      <c r="B93" s="38"/>
+      <c r="C93" s="38"/>
+      <c r="D93" s="38"/>
+      <c r="E93" s="38"/>
+      <c r="F93" s="38"/>
+      <c r="G93" s="38"/>
+      <c r="H93" s="38"/>
+      <c r="I93" s="38"/>
+      <c r="J93" s="38"/>
+      <c r="K93" s="38"/>
+      <c r="L93" s="38"/>
+      <c r="M93" s="38"/>
+      <c r="N93" s="38"/>
+      <c r="O93" s="38"/>
+      <c r="P93" s="38"/>
+      <c r="Q93" s="38"/>
+      <c r="R93" s="38"/>
+      <c r="S93" s="38"/>
+      <c r="T93" s="38"/>
+      <c r="U93" s="38"/>
+      <c r="V93" s="38"/>
+      <c r="W93" s="38"/>
+      <c r="X93" s="38"/>
+      <c r="Y93" s="38"/>
+      <c r="Z93" s="38"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="38"/>
+      <c r="B94" s="38"/>
+      <c r="C94" s="38"/>
+      <c r="D94" s="38"/>
+      <c r="E94" s="38"/>
+      <c r="F94" s="38"/>
+      <c r="G94" s="38"/>
+      <c r="H94" s="38"/>
+      <c r="I94" s="38"/>
+      <c r="J94" s="38"/>
+      <c r="K94" s="38"/>
+      <c r="L94" s="38"/>
+      <c r="M94" s="38"/>
+      <c r="N94" s="38"/>
+      <c r="O94" s="38"/>
+      <c r="P94" s="38"/>
+      <c r="Q94" s="38"/>
+      <c r="R94" s="38"/>
+      <c r="S94" s="38"/>
+      <c r="T94" s="38"/>
+      <c r="U94" s="38"/>
+      <c r="V94" s="38"/>
+      <c r="W94" s="38"/>
+      <c r="X94" s="38"/>
+      <c r="Y94" s="38"/>
+      <c r="Z94" s="38"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="38"/>
+      <c r="B95" s="38"/>
+      <c r="C95" s="38"/>
+      <c r="D95" s="38"/>
+      <c r="E95" s="38"/>
+      <c r="F95" s="38"/>
+      <c r="G95" s="38"/>
+      <c r="H95" s="38"/>
+      <c r="I95" s="38"/>
+      <c r="J95" s="38"/>
+      <c r="K95" s="38"/>
+      <c r="L95" s="38"/>
+      <c r="M95" s="38"/>
+      <c r="N95" s="38"/>
+      <c r="O95" s="38"/>
+      <c r="P95" s="38"/>
+      <c r="Q95" s="38"/>
+      <c r="R95" s="38"/>
+      <c r="S95" s="38"/>
+      <c r="T95" s="38"/>
+      <c r="U95" s="38"/>
+      <c r="V95" s="38"/>
+      <c r="W95" s="38"/>
+      <c r="X95" s="38"/>
+      <c r="Y95" s="38"/>
+      <c r="Z95" s="38"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="38"/>
+      <c r="B96" s="38"/>
+      <c r="C96" s="38"/>
+      <c r="D96" s="38"/>
+      <c r="E96" s="38"/>
+      <c r="F96" s="38"/>
+      <c r="G96" s="38"/>
+      <c r="H96" s="38"/>
+      <c r="I96" s="38"/>
+      <c r="J96" s="38"/>
+      <c r="K96" s="38"/>
+      <c r="L96" s="38"/>
+      <c r="M96" s="38"/>
+      <c r="N96" s="38"/>
+      <c r="O96" s="38"/>
+      <c r="P96" s="38"/>
+      <c r="Q96" s="38"/>
+      <c r="R96" s="38"/>
+      <c r="S96" s="38"/>
+      <c r="T96" s="38"/>
+      <c r="U96" s="38"/>
+      <c r="V96" s="38"/>
+      <c r="W96" s="38"/>
+      <c r="X96" s="38"/>
+      <c r="Y96" s="38"/>
+      <c r="Z96" s="38"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="38"/>
+      <c r="B97" s="38"/>
+      <c r="C97" s="38"/>
+      <c r="D97" s="38"/>
+      <c r="E97" s="38"/>
+      <c r="F97" s="38"/>
+      <c r="G97" s="38"/>
+      <c r="H97" s="38"/>
+      <c r="I97" s="38"/>
+      <c r="J97" s="38"/>
+      <c r="K97" s="38"/>
+      <c r="L97" s="38"/>
+      <c r="M97" s="38"/>
+      <c r="N97" s="38"/>
+      <c r="O97" s="38"/>
+      <c r="P97" s="38"/>
+      <c r="Q97" s="38"/>
+      <c r="R97" s="38"/>
+      <c r="S97" s="38"/>
+      <c r="T97" s="38"/>
+      <c r="U97" s="38"/>
+      <c r="V97" s="38"/>
+      <c r="W97" s="38"/>
+      <c r="X97" s="38"/>
+      <c r="Y97" s="38"/>
+      <c r="Z97" s="38"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="38"/>
+      <c r="B98" s="38"/>
+      <c r="C98" s="38"/>
+      <c r="D98" s="38"/>
+      <c r="E98" s="38"/>
+      <c r="F98" s="38"/>
+      <c r="G98" s="38"/>
+      <c r="H98" s="38"/>
+      <c r="I98" s="38"/>
+      <c r="J98" s="38"/>
+      <c r="K98" s="38"/>
+      <c r="L98" s="38"/>
+      <c r="M98" s="38"/>
+      <c r="N98" s="38"/>
+      <c r="O98" s="38"/>
+      <c r="P98" s="38"/>
+      <c r="Q98" s="38"/>
+      <c r="R98" s="38"/>
+      <c r="S98" s="38"/>
+      <c r="T98" s="38"/>
+      <c r="U98" s="38"/>
+      <c r="V98" s="38"/>
+      <c r="W98" s="38"/>
+      <c r="X98" s="38"/>
+      <c r="Y98" s="38"/>
+      <c r="Z98" s="38"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="38"/>
+      <c r="B99" s="38"/>
+      <c r="C99" s="38"/>
+      <c r="D99" s="38"/>
+      <c r="E99" s="38"/>
+      <c r="F99" s="38"/>
+      <c r="G99" s="38"/>
+      <c r="H99" s="38"/>
+      <c r="I99" s="38"/>
+      <c r="J99" s="38"/>
+      <c r="K99" s="38"/>
+      <c r="L99" s="38"/>
+      <c r="M99" s="38"/>
+      <c r="N99" s="38"/>
+      <c r="O99" s="38"/>
+      <c r="P99" s="38"/>
+      <c r="Q99" s="38"/>
+      <c r="R99" s="38"/>
+      <c r="S99" s="38"/>
+      <c r="T99" s="38"/>
+      <c r="U99" s="38"/>
+      <c r="V99" s="38"/>
+      <c r="W99" s="38"/>
+      <c r="X99" s="38"/>
+      <c r="Y99" s="38"/>
+      <c r="Z99" s="38"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="38"/>
+      <c r="B100" s="38"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="38"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="38"/>
+      <c r="H100" s="38"/>
+      <c r="I100" s="38"/>
+      <c r="J100" s="38"/>
+      <c r="K100" s="38"/>
+      <c r="L100" s="38"/>
+      <c r="M100" s="38"/>
+      <c r="N100" s="38"/>
+      <c r="O100" s="38"/>
+      <c r="P100" s="38"/>
+      <c r="Q100" s="38"/>
+      <c r="R100" s="38"/>
+      <c r="S100" s="38"/>
+      <c r="T100" s="38"/>
+      <c r="U100" s="38"/>
+      <c r="V100" s="38"/>
+      <c r="W100" s="38"/>
+      <c r="X100" s="38"/>
+      <c r="Y100" s="38"/>
+      <c r="Z100" s="38"/>
+    </row>
+    <row r="101">
+      <c r="D101" s="39"/>
+    </row>
+    <row r="102">
+      <c r="D102" s="39"/>
+    </row>
+    <row r="103">
+      <c r="D103" s="39"/>
+    </row>
+    <row r="104">
+      <c r="D104" s="39"/>
+    </row>
+    <row r="105">
+      <c r="D105" s="39"/>
+    </row>
+    <row r="106">
+      <c r="D106" s="39"/>
+    </row>
+    <row r="107">
+      <c r="D107" s="39"/>
+    </row>
+    <row r="108">
+      <c r="D108" s="39"/>
+    </row>
+    <row r="109">
+      <c r="D109" s="39"/>
+    </row>
+    <row r="110">
+      <c r="D110" s="39"/>
+    </row>
+    <row r="111">
+      <c r="D111" s="39"/>
+    </row>
+    <row r="112">
+      <c r="D112" s="39"/>
+    </row>
+    <row r="113">
+      <c r="D113" s="39"/>
+    </row>
+    <row r="114">
+      <c r="D114" s="39"/>
+    </row>
+    <row r="115">
+      <c r="D115" s="39"/>
+    </row>
+    <row r="116">
+      <c r="D116" s="39"/>
+    </row>
+    <row r="117">
+      <c r="D117" s="39"/>
+    </row>
+    <row r="118">
+      <c r="D118" s="39"/>
+    </row>
+    <row r="119">
+      <c r="D119" s="39"/>
+    </row>
+    <row r="120">
+      <c r="D120" s="39"/>
+    </row>
+    <row r="121">
+      <c r="D121" s="39"/>
+    </row>
+    <row r="122">
+      <c r="D122" s="39"/>
+    </row>
+    <row r="123">
+      <c r="D123" s="39"/>
+    </row>
+    <row r="124">
+      <c r="D124" s="39"/>
+    </row>
+    <row r="125">
+      <c r="D125" s="39"/>
+    </row>
+    <row r="126">
+      <c r="D126" s="39"/>
+    </row>
+    <row r="127">
+      <c r="D127" s="39"/>
+    </row>
+    <row r="128">
+      <c r="D128" s="39"/>
+    </row>
+    <row r="129">
+      <c r="D129" s="39"/>
+    </row>
+    <row r="130">
+      <c r="D130" s="39"/>
+    </row>
+    <row r="131">
+      <c r="D131" s="39"/>
+    </row>
+    <row r="132">
+      <c r="D132" s="39"/>
+    </row>
+    <row r="133">
+      <c r="D133" s="39"/>
+    </row>
+    <row r="134">
+      <c r="D134" s="39"/>
+    </row>
+    <row r="135">
+      <c r="D135" s="39"/>
+    </row>
+    <row r="136">
+      <c r="D136" s="39"/>
+    </row>
+    <row r="137">
+      <c r="D137" s="39"/>
+    </row>
+    <row r="138">
+      <c r="D138" s="39"/>
+    </row>
+    <row r="139">
+      <c r="D139" s="39"/>
+    </row>
+    <row r="140">
+      <c r="D140" s="39"/>
+    </row>
+    <row r="141">
+      <c r="D141" s="39"/>
+    </row>
+    <row r="142">
+      <c r="D142" s="39"/>
+    </row>
+    <row r="143">
+      <c r="D143" s="39"/>
+    </row>
+    <row r="144">
+      <c r="D144" s="39"/>
+    </row>
+    <row r="145">
+      <c r="D145" s="39"/>
+    </row>
+    <row r="146">
+      <c r="D146" s="39"/>
+    </row>
+    <row r="147">
+      <c r="D147" s="39"/>
+    </row>
+    <row r="148">
+      <c r="D148" s="39"/>
+    </row>
+    <row r="149">
+      <c r="D149" s="39"/>
+    </row>
+    <row r="150">
+      <c r="D150" s="39"/>
+    </row>
+    <row r="151">
+      <c r="D151" s="39"/>
+    </row>
+    <row r="152">
+      <c r="D152" s="39"/>
+    </row>
+    <row r="153">
+      <c r="D153" s="39"/>
+    </row>
+    <row r="154">
+      <c r="D154" s="39"/>
+    </row>
+    <row r="155">
+      <c r="D155" s="39"/>
+    </row>
+    <row r="156">
+      <c r="D156" s="39"/>
+    </row>
+    <row r="157">
+      <c r="D157" s="39"/>
+    </row>
+    <row r="158">
+      <c r="D158" s="39"/>
+    </row>
+    <row r="159">
+      <c r="D159" s="39"/>
+    </row>
+    <row r="160">
+      <c r="D160" s="39"/>
+    </row>
+    <row r="161">
+      <c r="D161" s="39"/>
+    </row>
+    <row r="162">
+      <c r="D162" s="39"/>
+    </row>
+    <row r="163">
+      <c r="D163" s="39"/>
+    </row>
+    <row r="164">
+      <c r="D164" s="39"/>
+    </row>
+    <row r="165">
+      <c r="D165" s="39"/>
+    </row>
+    <row r="166">
+      <c r="D166" s="39"/>
+    </row>
+    <row r="167">
+      <c r="D167" s="39"/>
+    </row>
+    <row r="168">
+      <c r="D168" s="39"/>
+    </row>
+    <row r="169">
+      <c r="D169" s="39"/>
+    </row>
+    <row r="170">
+      <c r="D170" s="39"/>
+    </row>
+    <row r="171">
+      <c r="D171" s="39"/>
+    </row>
+    <row r="172">
+      <c r="D172" s="39"/>
+    </row>
+    <row r="173">
+      <c r="D173" s="39"/>
+    </row>
+    <row r="174">
+      <c r="D174" s="39"/>
+    </row>
+    <row r="175">
+      <c r="D175" s="39"/>
+    </row>
+    <row r="176">
+      <c r="D176" s="39"/>
+    </row>
+    <row r="177">
+      <c r="D177" s="39"/>
+    </row>
+    <row r="178">
+      <c r="D178" s="39"/>
+    </row>
+    <row r="179">
+      <c r="D179" s="39"/>
+    </row>
+    <row r="180">
+      <c r="D180" s="39"/>
+    </row>
+    <row r="181">
+      <c r="D181" s="39"/>
+    </row>
+    <row r="182">
+      <c r="D182" s="39"/>
+    </row>
+    <row r="183">
+      <c r="D183" s="39"/>
+    </row>
+    <row r="184">
+      <c r="D184" s="39"/>
+    </row>
+    <row r="185">
+      <c r="D185" s="39"/>
+    </row>
+    <row r="186">
+      <c r="D186" s="39"/>
+    </row>
+    <row r="187">
+      <c r="D187" s="39"/>
+    </row>
+    <row r="188">
+      <c r="D188" s="39"/>
+    </row>
+    <row r="189">
+      <c r="D189" s="39"/>
+    </row>
+    <row r="190">
+      <c r="D190" s="39"/>
+    </row>
+    <row r="191">
+      <c r="D191" s="39"/>
+    </row>
+    <row r="192">
+      <c r="D192" s="39"/>
+    </row>
+    <row r="193">
+      <c r="D193" s="39"/>
+    </row>
+    <row r="194">
+      <c r="D194" s="39"/>
+    </row>
+    <row r="195">
+      <c r="D195" s="39"/>
+    </row>
+    <row r="196">
+      <c r="D196" s="39"/>
+    </row>
+    <row r="197">
+      <c r="D197" s="39"/>
+    </row>
+    <row r="198">
+      <c r="D198" s="39"/>
+    </row>
+    <row r="199">
+      <c r="D199" s="39"/>
+    </row>
+    <row r="200">
+      <c r="D200" s="39"/>
+    </row>
+    <row r="201">
+      <c r="D201" s="39"/>
+    </row>
+    <row r="202">
+      <c r="D202" s="39"/>
+    </row>
+    <row r="203">
+      <c r="D203" s="39"/>
+    </row>
+    <row r="204">
+      <c r="D204" s="39"/>
+    </row>
+    <row r="205">
+      <c r="D205" s="39"/>
+    </row>
+    <row r="206">
+      <c r="D206" s="39"/>
+    </row>
+    <row r="207">
+      <c r="D207" s="39"/>
+    </row>
+    <row r="208">
+      <c r="D208" s="39"/>
+    </row>
+    <row r="209">
+      <c r="D209" s="39"/>
+    </row>
+    <row r="210">
+      <c r="D210" s="39"/>
+    </row>
+    <row r="211">
+      <c r="D211" s="39"/>
+    </row>
+    <row r="212">
+      <c r="D212" s="39"/>
+    </row>
+    <row r="213">
+      <c r="D213" s="39"/>
+    </row>
+    <row r="214">
+      <c r="D214" s="39"/>
+    </row>
+    <row r="215">
+      <c r="D215" s="39"/>
+    </row>
+    <row r="216">
+      <c r="D216" s="39"/>
+    </row>
+    <row r="217">
+      <c r="D217" s="39"/>
+    </row>
+    <row r="218">
+      <c r="D218" s="39"/>
+    </row>
+    <row r="219">
+      <c r="D219" s="39"/>
+    </row>
+    <row r="220">
+      <c r="D220" s="39"/>
+    </row>
+    <row r="221">
+      <c r="D221" s="39"/>
+    </row>
+    <row r="222">
+      <c r="D222" s="39"/>
+    </row>
+    <row r="223">
+      <c r="D223" s="39"/>
+    </row>
+    <row r="224">
+      <c r="D224" s="39"/>
+    </row>
+    <row r="225">
+      <c r="D225" s="39"/>
+    </row>
+    <row r="226">
+      <c r="D226" s="39"/>
+    </row>
+    <row r="227">
+      <c r="D227" s="39"/>
+    </row>
+    <row r="228">
+      <c r="D228" s="39"/>
+    </row>
+    <row r="229">
+      <c r="D229" s="39"/>
+    </row>
+    <row r="230">
+      <c r="D230" s="39"/>
+    </row>
+    <row r="231">
+      <c r="D231" s="39"/>
+    </row>
+    <row r="232">
+      <c r="D232" s="39"/>
+    </row>
+    <row r="233">
+      <c r="D233" s="39"/>
+    </row>
+    <row r="234">
+      <c r="D234" s="39"/>
+    </row>
+    <row r="235">
+      <c r="D235" s="39"/>
+    </row>
+    <row r="236">
+      <c r="D236" s="39"/>
+    </row>
+    <row r="237">
+      <c r="D237" s="39"/>
+    </row>
+    <row r="238">
+      <c r="D238" s="39"/>
+    </row>
+    <row r="239">
+      <c r="D239" s="39"/>
+    </row>
+    <row r="240">
+      <c r="D240" s="39"/>
+    </row>
+    <row r="241">
+      <c r="D241" s="39"/>
+    </row>
+    <row r="242">
+      <c r="D242" s="39"/>
+    </row>
+    <row r="243">
+      <c r="D243" s="39"/>
+    </row>
+    <row r="244">
+      <c r="D244" s="39"/>
+    </row>
+    <row r="245">
+      <c r="D245" s="39"/>
+    </row>
+    <row r="246">
+      <c r="D246" s="39"/>
+    </row>
+    <row r="247">
+      <c r="D247" s="39"/>
+    </row>
+    <row r="248">
+      <c r="D248" s="39"/>
+    </row>
+    <row r="249">
+      <c r="D249" s="39"/>
+    </row>
+    <row r="250">
+      <c r="D250" s="39"/>
+    </row>
+    <row r="251">
+      <c r="D251" s="39"/>
+    </row>
+    <row r="252">
+      <c r="D252" s="39"/>
+    </row>
+    <row r="253">
+      <c r="D253" s="39"/>
+    </row>
+    <row r="254">
+      <c r="D254" s="39"/>
+    </row>
+    <row r="255">
+      <c r="D255" s="39"/>
+    </row>
+    <row r="256">
+      <c r="D256" s="39"/>
+    </row>
+    <row r="257">
+      <c r="D257" s="39"/>
+    </row>
+    <row r="258">
+      <c r="D258" s="39"/>
+    </row>
+    <row r="259">
+      <c r="D259" s="39"/>
+    </row>
+    <row r="260">
+      <c r="D260" s="39"/>
+    </row>
+    <row r="261">
+      <c r="D261" s="39"/>
+    </row>
+    <row r="262">
+      <c r="D262" s="39"/>
+    </row>
+    <row r="263">
+      <c r="D263" s="39"/>
+    </row>
+    <row r="264">
+      <c r="D264" s="39"/>
+    </row>
+    <row r="265">
+      <c r="D265" s="39"/>
+    </row>
+    <row r="266">
+      <c r="D266" s="39"/>
+    </row>
+    <row r="267">
+      <c r="D267" s="39"/>
+    </row>
+    <row r="268">
+      <c r="D268" s="39"/>
+    </row>
+    <row r="269">
+      <c r="D269" s="39"/>
+    </row>
+    <row r="270">
+      <c r="D270" s="39"/>
+    </row>
+    <row r="271">
+      <c r="D271" s="39"/>
+    </row>
+    <row r="272">
+      <c r="D272" s="39"/>
+    </row>
+    <row r="273">
+      <c r="D273" s="39"/>
+    </row>
+    <row r="274">
+      <c r="D274" s="39"/>
+    </row>
+    <row r="275">
+      <c r="D275" s="39"/>
+    </row>
+    <row r="276">
+      <c r="D276" s="39"/>
+    </row>
+    <row r="277">
+      <c r="D277" s="39"/>
+    </row>
+    <row r="278">
+      <c r="D278" s="39"/>
+    </row>
+    <row r="279">
+      <c r="D279" s="39"/>
+    </row>
+    <row r="280">
+      <c r="D280" s="39"/>
+    </row>
+    <row r="281">
+      <c r="D281" s="39"/>
+    </row>
+    <row r="282">
+      <c r="D282" s="39"/>
+    </row>
+    <row r="283">
+      <c r="D283" s="39"/>
+    </row>
+    <row r="284">
+      <c r="D284" s="39"/>
+    </row>
+    <row r="285">
+      <c r="D285" s="39"/>
+    </row>
+    <row r="286">
+      <c r="D286" s="39"/>
+    </row>
+    <row r="287">
+      <c r="D287" s="39"/>
+    </row>
+    <row r="288">
+      <c r="D288" s="39"/>
+    </row>
+    <row r="289">
+      <c r="D289" s="39"/>
+    </row>
+    <row r="290">
+      <c r="D290" s="39"/>
+    </row>
+    <row r="291">
+      <c r="D291" s="39"/>
+    </row>
+    <row r="292">
+      <c r="D292" s="39"/>
+    </row>
+    <row r="293">
+      <c r="D293" s="39"/>
+    </row>
+    <row r="294">
+      <c r="D294" s="39"/>
+    </row>
+    <row r="295">
+      <c r="D295" s="39"/>
+    </row>
+    <row r="296">
+      <c r="D296" s="39"/>
+    </row>
+    <row r="297">
+      <c r="D297" s="39"/>
+    </row>
+    <row r="298">
+      <c r="D298" s="39"/>
+    </row>
+    <row r="299">
+      <c r="D299" s="39"/>
+    </row>
+    <row r="300">
+      <c r="D300" s="39"/>
+    </row>
+    <row r="301">
+      <c r="D301" s="39"/>
+    </row>
+    <row r="302">
+      <c r="D302" s="39"/>
+    </row>
+    <row r="303">
+      <c r="D303" s="39"/>
+    </row>
+    <row r="304">
+      <c r="D304" s="39"/>
+    </row>
+    <row r="305">
+      <c r="D305" s="39"/>
+    </row>
+    <row r="306">
+      <c r="D306" s="39"/>
+    </row>
+    <row r="307">
+      <c r="D307" s="39"/>
+    </row>
+    <row r="308">
+      <c r="D308" s="39"/>
+    </row>
+    <row r="309">
+      <c r="D309" s="39"/>
+    </row>
+    <row r="310">
+      <c r="D310" s="39"/>
+    </row>
+    <row r="311">
+      <c r="D311" s="39"/>
+    </row>
+    <row r="312">
+      <c r="D312" s="39"/>
+    </row>
+    <row r="313">
+      <c r="D313" s="39"/>
+    </row>
+    <row r="314">
+      <c r="D314" s="39"/>
+    </row>
+    <row r="315">
+      <c r="D315" s="39"/>
+    </row>
+    <row r="316">
+      <c r="D316" s="39"/>
+    </row>
+    <row r="317">
+      <c r="D317" s="39"/>
+    </row>
+    <row r="318">
+      <c r="D318" s="39"/>
+    </row>
+    <row r="319">
+      <c r="D319" s="39"/>
+    </row>
+    <row r="320">
+      <c r="D320" s="39"/>
+    </row>
+    <row r="321">
+      <c r="D321" s="39"/>
+    </row>
+    <row r="322">
+      <c r="D322" s="39"/>
+    </row>
+    <row r="323">
+      <c r="D323" s="39"/>
+    </row>
+    <row r="324">
+      <c r="D324" s="39"/>
+    </row>
+    <row r="325">
+      <c r="D325" s="39"/>
+    </row>
+    <row r="326">
+      <c r="D326" s="39"/>
+    </row>
+    <row r="327">
+      <c r="D327" s="39"/>
+    </row>
+    <row r="328">
+      <c r="D328" s="39"/>
+    </row>
+    <row r="329">
+      <c r="D329" s="39"/>
+    </row>
+    <row r="330">
+      <c r="D330" s="39"/>
+    </row>
+    <row r="331">
+      <c r="D331" s="39"/>
+    </row>
+    <row r="332">
+      <c r="D332" s="39"/>
+    </row>
+    <row r="333">
+      <c r="D333" s="39"/>
+    </row>
+    <row r="334">
+      <c r="D334" s="39"/>
+    </row>
+    <row r="335">
+      <c r="D335" s="39"/>
+    </row>
+    <row r="336">
+      <c r="D336" s="39"/>
+    </row>
+    <row r="337">
+      <c r="D337" s="39"/>
+    </row>
+    <row r="338">
+      <c r="D338" s="39"/>
+    </row>
+    <row r="339">
+      <c r="D339" s="39"/>
+    </row>
+    <row r="340">
+      <c r="D340" s="39"/>
+    </row>
+    <row r="341">
+      <c r="D341" s="39"/>
+    </row>
+    <row r="342">
+      <c r="D342" s="39"/>
+    </row>
+    <row r="343">
+      <c r="D343" s="39"/>
+    </row>
+    <row r="344">
+      <c r="D344" s="39"/>
+    </row>
+    <row r="345">
+      <c r="D345" s="39"/>
+    </row>
+    <row r="346">
+      <c r="D346" s="39"/>
+    </row>
+    <row r="347">
+      <c r="D347" s="39"/>
+    </row>
+    <row r="348">
+      <c r="D348" s="39"/>
+    </row>
+    <row r="349">
+      <c r="D349" s="39"/>
+    </row>
+    <row r="350">
+      <c r="D350" s="39"/>
+    </row>
+    <row r="351">
+      <c r="D351" s="39"/>
+    </row>
+    <row r="352">
+      <c r="D352" s="39"/>
+    </row>
+    <row r="353">
+      <c r="D353" s="39"/>
+    </row>
+    <row r="354">
+      <c r="D354" s="39"/>
+    </row>
+    <row r="355">
+      <c r="D355" s="39"/>
+    </row>
+    <row r="356">
+      <c r="D356" s="39"/>
+    </row>
+    <row r="357">
+      <c r="D357" s="39"/>
+    </row>
+    <row r="358">
+      <c r="D358" s="39"/>
+    </row>
+    <row r="359">
+      <c r="D359" s="39"/>
+    </row>
+    <row r="360">
+      <c r="D360" s="39"/>
+    </row>
+    <row r="361">
+      <c r="D361" s="39"/>
+    </row>
+    <row r="362">
+      <c r="D362" s="39"/>
+    </row>
+    <row r="363">
+      <c r="D363" s="39"/>
+    </row>
+    <row r="364">
+      <c r="D364" s="39"/>
+    </row>
+    <row r="365">
+      <c r="D365" s="39"/>
+    </row>
+    <row r="366">
+      <c r="D366" s="39"/>
+    </row>
+    <row r="367">
+      <c r="D367" s="39"/>
+    </row>
+    <row r="368">
+      <c r="D368" s="39"/>
+    </row>
+    <row r="369">
+      <c r="D369" s="39"/>
+    </row>
+    <row r="370">
+      <c r="D370" s="39"/>
+    </row>
+    <row r="371">
+      <c r="D371" s="39"/>
+    </row>
+    <row r="372">
+      <c r="D372" s="39"/>
+    </row>
+    <row r="373">
+      <c r="D373" s="39"/>
+    </row>
+    <row r="374">
+      <c r="D374" s="39"/>
+    </row>
+    <row r="375">
+      <c r="D375" s="39"/>
+    </row>
+    <row r="376">
+      <c r="D376" s="39"/>
+    </row>
+    <row r="377">
+      <c r="D377" s="39"/>
+    </row>
+    <row r="378">
+      <c r="D378" s="39"/>
+    </row>
+    <row r="379">
+      <c r="D379" s="39"/>
+    </row>
+    <row r="380">
+      <c r="D380" s="39"/>
+    </row>
+    <row r="381">
+      <c r="D381" s="39"/>
+    </row>
+    <row r="382">
+      <c r="D382" s="39"/>
+    </row>
+    <row r="383">
+      <c r="D383" s="39"/>
+    </row>
+    <row r="384">
+      <c r="D384" s="39"/>
+    </row>
+    <row r="385">
+      <c r="D385" s="39"/>
+    </row>
+    <row r="386">
+      <c r="D386" s="39"/>
+    </row>
+    <row r="387">
+      <c r="D387" s="39"/>
+    </row>
+    <row r="388">
+      <c r="D388" s="39"/>
+    </row>
+    <row r="389">
+      <c r="D389" s="39"/>
+    </row>
+    <row r="390">
+      <c r="D390" s="39"/>
+    </row>
+    <row r="391">
+      <c r="D391" s="39"/>
+    </row>
+    <row r="392">
+      <c r="D392" s="39"/>
+    </row>
+    <row r="393">
+      <c r="D393" s="39"/>
+    </row>
+    <row r="394">
+      <c r="D394" s="39"/>
+    </row>
+    <row r="395">
+      <c r="D395" s="39"/>
+    </row>
+    <row r="396">
+      <c r="D396" s="39"/>
+    </row>
+    <row r="397">
+      <c r="D397" s="39"/>
+    </row>
+    <row r="398">
+      <c r="D398" s="39"/>
+    </row>
+    <row r="399">
+      <c r="D399" s="39"/>
+    </row>
+    <row r="400">
+      <c r="D400" s="39"/>
+    </row>
+    <row r="401">
+      <c r="D401" s="39"/>
+    </row>
+    <row r="402">
+      <c r="D402" s="39"/>
+    </row>
+    <row r="403">
+      <c r="D403" s="39"/>
+    </row>
+    <row r="404">
+      <c r="D404" s="39"/>
+    </row>
+    <row r="405">
+      <c r="D405" s="39"/>
+    </row>
+    <row r="406">
+      <c r="D406" s="39"/>
+    </row>
+    <row r="407">
+      <c r="D407" s="39"/>
+    </row>
+    <row r="408">
+      <c r="D408" s="39"/>
+    </row>
+    <row r="409">
+      <c r="D409" s="39"/>
+    </row>
+    <row r="410">
+      <c r="D410" s="39"/>
+    </row>
+    <row r="411">
+      <c r="D411" s="39"/>
+    </row>
+    <row r="412">
+      <c r="D412" s="39"/>
+    </row>
+    <row r="413">
+      <c r="D413" s="39"/>
+    </row>
+    <row r="414">
+      <c r="D414" s="39"/>
+    </row>
+    <row r="415">
+      <c r="D415" s="39"/>
+    </row>
+    <row r="416">
+      <c r="D416" s="39"/>
+    </row>
+    <row r="417">
+      <c r="D417" s="39"/>
+    </row>
+    <row r="418">
+      <c r="D418" s="39"/>
+    </row>
+    <row r="419">
+      <c r="D419" s="39"/>
+    </row>
+    <row r="420">
+      <c r="D420" s="39"/>
+    </row>
+    <row r="421">
+      <c r="D421" s="39"/>
+    </row>
+    <row r="422">
+      <c r="D422" s="39"/>
+    </row>
+    <row r="423">
+      <c r="D423" s="39"/>
+    </row>
+    <row r="424">
+      <c r="D424" s="39"/>
+    </row>
+    <row r="425">
+      <c r="D425" s="39"/>
+    </row>
+    <row r="426">
+      <c r="D426" s="39"/>
+    </row>
+    <row r="427">
+      <c r="D427" s="39"/>
+    </row>
+    <row r="428">
+      <c r="D428" s="39"/>
+    </row>
+    <row r="429">
+      <c r="D429" s="39"/>
+    </row>
+    <row r="430">
+      <c r="D430" s="39"/>
+    </row>
+    <row r="431">
+      <c r="D431" s="39"/>
+    </row>
+    <row r="432">
+      <c r="D432" s="39"/>
+    </row>
+    <row r="433">
+      <c r="D433" s="39"/>
+    </row>
+    <row r="434">
+      <c r="D434" s="39"/>
+    </row>
+    <row r="435">
+      <c r="D435" s="39"/>
+    </row>
+    <row r="436">
+      <c r="D436" s="39"/>
+    </row>
+    <row r="437">
+      <c r="D437" s="39"/>
+    </row>
+    <row r="438">
+      <c r="D438" s="39"/>
+    </row>
+    <row r="439">
+      <c r="D439" s="39"/>
+    </row>
+    <row r="440">
+      <c r="D440" s="39"/>
+    </row>
+    <row r="441">
+      <c r="D441" s="39"/>
+    </row>
+    <row r="442">
+      <c r="D442" s="39"/>
+    </row>
+    <row r="443">
+      <c r="D443" s="39"/>
+    </row>
+    <row r="444">
+      <c r="D444" s="39"/>
+    </row>
+    <row r="445">
+      <c r="D445" s="39"/>
+    </row>
+    <row r="446">
+      <c r="D446" s="39"/>
+    </row>
+    <row r="447">
+      <c r="D447" s="39"/>
+    </row>
+    <row r="448">
+      <c r="D448" s="39"/>
+    </row>
+    <row r="449">
+      <c r="D449" s="39"/>
+    </row>
+    <row r="450">
+      <c r="D450" s="39"/>
+    </row>
+    <row r="451">
+      <c r="D451" s="39"/>
+    </row>
+    <row r="452">
+      <c r="D452" s="39"/>
+    </row>
+    <row r="453">
+      <c r="D453" s="39"/>
+    </row>
+    <row r="454">
+      <c r="D454" s="39"/>
+    </row>
+    <row r="455">
+      <c r="D455" s="39"/>
+    </row>
+    <row r="456">
+      <c r="D456" s="39"/>
+    </row>
+    <row r="457">
+      <c r="D457" s="39"/>
+    </row>
+    <row r="458">
+      <c r="D458" s="39"/>
+    </row>
+    <row r="459">
+      <c r="D459" s="39"/>
+    </row>
+    <row r="460">
+      <c r="D460" s="39"/>
+    </row>
+    <row r="461">
+      <c r="D461" s="39"/>
+    </row>
+    <row r="462">
+      <c r="D462" s="39"/>
+    </row>
+    <row r="463">
+      <c r="D463" s="39"/>
+    </row>
+    <row r="464">
+      <c r="D464" s="39"/>
+    </row>
+    <row r="465">
+      <c r="D465" s="39"/>
+    </row>
+    <row r="466">
+      <c r="D466" s="39"/>
+    </row>
+    <row r="467">
+      <c r="D467" s="39"/>
+    </row>
+    <row r="468">
+      <c r="D468" s="39"/>
+    </row>
+    <row r="469">
+      <c r="D469" s="39"/>
+    </row>
+    <row r="470">
+      <c r="D470" s="39"/>
+    </row>
+    <row r="471">
+      <c r="D471" s="39"/>
+    </row>
+    <row r="472">
+      <c r="D472" s="39"/>
+    </row>
+    <row r="473">
+      <c r="D473" s="39"/>
+    </row>
+    <row r="474">
+      <c r="D474" s="39"/>
+    </row>
+    <row r="475">
+      <c r="D475" s="39"/>
+    </row>
+    <row r="476">
+      <c r="D476" s="39"/>
+    </row>
+    <row r="477">
+      <c r="D477" s="39"/>
+    </row>
+    <row r="478">
+      <c r="D478" s="39"/>
+    </row>
+    <row r="479">
+      <c r="D479" s="39"/>
+    </row>
+    <row r="480">
+      <c r="D480" s="39"/>
+    </row>
+    <row r="481">
+      <c r="D481" s="39"/>
+    </row>
+    <row r="482">
+      <c r="D482" s="39"/>
+    </row>
+    <row r="483">
+      <c r="D483" s="39"/>
+    </row>
+    <row r="484">
+      <c r="D484" s="39"/>
+    </row>
+    <row r="485">
+      <c r="D485" s="39"/>
+    </row>
+    <row r="486">
+      <c r="D486" s="39"/>
+    </row>
+    <row r="487">
+      <c r="D487" s="39"/>
+    </row>
+    <row r="488">
+      <c r="D488" s="39"/>
+    </row>
+    <row r="489">
+      <c r="D489" s="39"/>
+    </row>
+    <row r="490">
+      <c r="D490" s="39"/>
+    </row>
+    <row r="491">
+      <c r="D491" s="39"/>
+    </row>
+    <row r="492">
+      <c r="D492" s="39"/>
+    </row>
+    <row r="493">
+      <c r="D493" s="39"/>
+    </row>
+    <row r="494">
+      <c r="D494" s="39"/>
+    </row>
+    <row r="495">
+      <c r="D495" s="39"/>
+    </row>
+    <row r="496">
+      <c r="D496" s="39"/>
+    </row>
+    <row r="497">
+      <c r="D497" s="39"/>
+    </row>
+    <row r="498">
+      <c r="D498" s="39"/>
+    </row>
+    <row r="499">
+      <c r="D499" s="39"/>
+    </row>
+    <row r="500">
+      <c r="D500" s="39"/>
+    </row>
+    <row r="501">
+      <c r="D501" s="39"/>
+    </row>
+    <row r="502">
+      <c r="D502" s="39"/>
+    </row>
+    <row r="503">
+      <c r="D503" s="39"/>
+    </row>
+    <row r="504">
+      <c r="D504" s="39"/>
+    </row>
+    <row r="505">
+      <c r="D505" s="39"/>
+    </row>
+    <row r="506">
+      <c r="D506" s="39"/>
+    </row>
+    <row r="507">
+      <c r="D507" s="39"/>
+    </row>
+    <row r="508">
+      <c r="D508" s="39"/>
+    </row>
+    <row r="509">
+      <c r="D509" s="39"/>
+    </row>
+    <row r="510">
+      <c r="D510" s="39"/>
+    </row>
+    <row r="511">
+      <c r="D511" s="39"/>
+    </row>
+    <row r="512">
+      <c r="D512" s="39"/>
+    </row>
+    <row r="513">
+      <c r="D513" s="39"/>
+    </row>
+    <row r="514">
+      <c r="D514" s="39"/>
+    </row>
+    <row r="515">
+      <c r="D515" s="39"/>
+    </row>
+    <row r="516">
+      <c r="D516" s="39"/>
+    </row>
+    <row r="517">
+      <c r="D517" s="39"/>
+    </row>
+    <row r="518">
+      <c r="D518" s="39"/>
+    </row>
+    <row r="519">
+      <c r="D519" s="39"/>
+    </row>
+    <row r="520">
+      <c r="D520" s="39"/>
+    </row>
+    <row r="521">
+      <c r="D521" s="39"/>
+    </row>
+    <row r="522">
+      <c r="D522" s="39"/>
+    </row>
+    <row r="523">
+      <c r="D523" s="39"/>
+    </row>
+    <row r="524">
+      <c r="D524" s="39"/>
+    </row>
+    <row r="525">
+      <c r="D525" s="39"/>
+    </row>
+    <row r="526">
+      <c r="D526" s="39"/>
+    </row>
+    <row r="527">
+      <c r="D527" s="39"/>
+    </row>
+    <row r="528">
+      <c r="D528" s="39"/>
+    </row>
+    <row r="529">
+      <c r="D529" s="39"/>
+    </row>
+    <row r="530">
+      <c r="D530" s="39"/>
+    </row>
+    <row r="531">
+      <c r="D531" s="39"/>
+    </row>
+    <row r="532">
+      <c r="D532" s="39"/>
+    </row>
+    <row r="533">
+      <c r="D533" s="39"/>
+    </row>
+    <row r="534">
+      <c r="D534" s="39"/>
+    </row>
+    <row r="535">
+      <c r="D535" s="39"/>
+    </row>
+    <row r="536">
+      <c r="D536" s="39"/>
+    </row>
+    <row r="537">
+      <c r="D537" s="39"/>
+    </row>
+    <row r="538">
+      <c r="D538" s="39"/>
+    </row>
+    <row r="539">
+      <c r="D539" s="39"/>
+    </row>
+    <row r="540">
+      <c r="D540" s="39"/>
+    </row>
+    <row r="541">
+      <c r="D541" s="39"/>
+    </row>
+    <row r="542">
+      <c r="D542" s="39"/>
+    </row>
+    <row r="543">
+      <c r="D543" s="39"/>
+    </row>
+    <row r="544">
+      <c r="D544" s="39"/>
+    </row>
+    <row r="545">
+      <c r="D545" s="39"/>
+    </row>
+    <row r="546">
+      <c r="D546" s="39"/>
+    </row>
+    <row r="547">
+      <c r="D547" s="39"/>
+    </row>
+    <row r="548">
+      <c r="D548" s="39"/>
+    </row>
+    <row r="549">
+      <c r="D549" s="39"/>
+    </row>
+    <row r="550">
+      <c r="D550" s="39"/>
+    </row>
+    <row r="551">
+      <c r="D551" s="39"/>
+    </row>
+    <row r="552">
+      <c r="D552" s="39"/>
+    </row>
+    <row r="553">
+      <c r="D553" s="39"/>
+    </row>
+    <row r="554">
+      <c r="D554" s="39"/>
+    </row>
+    <row r="555">
+      <c r="D555" s="39"/>
+    </row>
+    <row r="556">
+      <c r="D556" s="39"/>
+    </row>
+    <row r="557">
+      <c r="D557" s="39"/>
+    </row>
+    <row r="558">
+      <c r="D558" s="39"/>
+    </row>
+    <row r="559">
+      <c r="D559" s="39"/>
+    </row>
+    <row r="560">
+      <c r="D560" s="39"/>
+    </row>
+    <row r="561">
+      <c r="D561" s="39"/>
+    </row>
+    <row r="562">
+      <c r="D562" s="39"/>
+    </row>
+    <row r="563">
+      <c r="D563" s="39"/>
+    </row>
+    <row r="564">
+      <c r="D564" s="39"/>
+    </row>
+    <row r="565">
+      <c r="D565" s="39"/>
+    </row>
+    <row r="566">
+      <c r="D566" s="39"/>
+    </row>
+    <row r="567">
+      <c r="D567" s="39"/>
+    </row>
+    <row r="568">
+      <c r="D568" s="39"/>
+    </row>
+    <row r="569">
+      <c r="D569" s="39"/>
+    </row>
+    <row r="570">
+      <c r="D570" s="39"/>
+    </row>
+    <row r="571">
+      <c r="D571" s="39"/>
+    </row>
+    <row r="572">
+      <c r="D572" s="39"/>
+    </row>
+    <row r="573">
+      <c r="D573" s="39"/>
+    </row>
+    <row r="574">
+      <c r="D574" s="39"/>
+    </row>
+    <row r="575">
+      <c r="D575" s="39"/>
+    </row>
+    <row r="576">
+      <c r="D576" s="39"/>
+    </row>
+    <row r="577">
+      <c r="D577" s="39"/>
+    </row>
+    <row r="578">
+      <c r="D578" s="39"/>
+    </row>
+    <row r="579">
+      <c r="D579" s="39"/>
+    </row>
+    <row r="580">
+      <c r="D580" s="39"/>
+    </row>
+    <row r="581">
+      <c r="D581" s="39"/>
+    </row>
+    <row r="582">
+      <c r="D582" s="39"/>
+    </row>
+    <row r="583">
+      <c r="D583" s="39"/>
+    </row>
+    <row r="584">
+      <c r="D584" s="39"/>
+    </row>
+    <row r="585">
+      <c r="D585" s="39"/>
+    </row>
+    <row r="586">
+      <c r="D586" s="39"/>
+    </row>
+    <row r="587">
+      <c r="D587" s="39"/>
+    </row>
+    <row r="588">
+      <c r="D588" s="39"/>
+    </row>
+    <row r="589">
+      <c r="D589" s="39"/>
+    </row>
+    <row r="590">
+      <c r="D590" s="39"/>
+    </row>
+    <row r="591">
+      <c r="D591" s="39"/>
+    </row>
+    <row r="592">
+      <c r="D592" s="39"/>
+    </row>
+    <row r="593">
+      <c r="D593" s="39"/>
+    </row>
+    <row r="594">
+      <c r="D594" s="39"/>
+    </row>
+    <row r="595">
+      <c r="D595" s="39"/>
+    </row>
+    <row r="596">
+      <c r="D596" s="39"/>
+    </row>
+    <row r="597">
+      <c r="D597" s="39"/>
+    </row>
+    <row r="598">
+      <c r="D598" s="39"/>
+    </row>
+    <row r="599">
+      <c r="D599" s="39"/>
+    </row>
+    <row r="600">
+      <c r="D600" s="39"/>
+    </row>
+    <row r="601">
+      <c r="D601" s="39"/>
+    </row>
+    <row r="602">
+      <c r="D602" s="39"/>
+    </row>
+    <row r="603">
+      <c r="D603" s="39"/>
+    </row>
+    <row r="604">
+      <c r="D604" s="39"/>
+    </row>
+    <row r="605">
+      <c r="D605" s="39"/>
+    </row>
+    <row r="606">
+      <c r="D606" s="39"/>
+    </row>
+    <row r="607">
+      <c r="D607" s="39"/>
+    </row>
+    <row r="608">
+      <c r="D608" s="39"/>
+    </row>
+    <row r="609">
+      <c r="D609" s="39"/>
+    </row>
+    <row r="610">
+      <c r="D610" s="39"/>
+    </row>
+    <row r="611">
+      <c r="D611" s="39"/>
+    </row>
+    <row r="612">
+      <c r="D612" s="39"/>
+    </row>
+    <row r="613">
+      <c r="D613" s="39"/>
+    </row>
+    <row r="614">
+      <c r="D614" s="39"/>
+    </row>
+    <row r="615">
+      <c r="D615" s="39"/>
+    </row>
+    <row r="616">
+      <c r="D616" s="39"/>
+    </row>
+    <row r="617">
+      <c r="D617" s="39"/>
+    </row>
+    <row r="618">
+      <c r="D618" s="39"/>
+    </row>
+    <row r="619">
+      <c r="D619" s="39"/>
+    </row>
+    <row r="620">
+      <c r="D620" s="39"/>
+    </row>
+    <row r="621">
+      <c r="D621" s="39"/>
+    </row>
+    <row r="622">
+      <c r="D622" s="39"/>
+    </row>
+    <row r="623">
+      <c r="D623" s="39"/>
+    </row>
+    <row r="624">
+      <c r="D624" s="39"/>
+    </row>
+    <row r="625">
+      <c r="D625" s="39"/>
+    </row>
+    <row r="626">
+      <c r="D626" s="39"/>
+    </row>
+    <row r="627">
+      <c r="D627" s="39"/>
+    </row>
+    <row r="628">
+      <c r="D628" s="39"/>
+    </row>
+    <row r="629">
+      <c r="D629" s="39"/>
+    </row>
+    <row r="630">
+      <c r="D630" s="39"/>
+    </row>
+    <row r="631">
+      <c r="D631" s="39"/>
+    </row>
+    <row r="632">
+      <c r="D632" s="39"/>
+    </row>
+    <row r="633">
+      <c r="D633" s="39"/>
+    </row>
+    <row r="634">
+      <c r="D634" s="39"/>
+    </row>
+    <row r="635">
+      <c r="D635" s="39"/>
+    </row>
+    <row r="636">
+      <c r="D636" s="39"/>
+    </row>
+    <row r="637">
+      <c r="D637" s="39"/>
+    </row>
+    <row r="638">
+      <c r="D638" s="39"/>
+    </row>
+    <row r="639">
+      <c r="D639" s="39"/>
+    </row>
+    <row r="640">
+      <c r="D640" s="39"/>
+    </row>
+    <row r="641">
+      <c r="D641" s="39"/>
+    </row>
+    <row r="642">
+      <c r="D642" s="39"/>
+    </row>
+    <row r="643">
+      <c r="D643" s="39"/>
+    </row>
+    <row r="644">
+      <c r="D644" s="39"/>
+    </row>
+    <row r="645">
+      <c r="D645" s="39"/>
+    </row>
+    <row r="646">
+      <c r="D646" s="39"/>
+    </row>
+    <row r="647">
+      <c r="D647" s="39"/>
+    </row>
+    <row r="648">
+      <c r="D648" s="39"/>
+    </row>
+    <row r="649">
+      <c r="D649" s="39"/>
+    </row>
+    <row r="650">
+      <c r="D650" s="39"/>
+    </row>
+    <row r="651">
+      <c r="D651" s="39"/>
+    </row>
+    <row r="652">
+      <c r="D652" s="39"/>
+    </row>
+    <row r="653">
+      <c r="D653" s="39"/>
+    </row>
+    <row r="654">
+      <c r="D654" s="39"/>
+    </row>
+    <row r="655">
+      <c r="D655" s="39"/>
+    </row>
+    <row r="656">
+      <c r="D656" s="39"/>
+    </row>
+    <row r="657">
+      <c r="D657" s="39"/>
+    </row>
+    <row r="658">
+      <c r="D658" s="39"/>
+    </row>
+    <row r="659">
+      <c r="D659" s="39"/>
+    </row>
+    <row r="660">
+      <c r="D660" s="39"/>
+    </row>
+    <row r="661">
+      <c r="D661" s="39"/>
+    </row>
+    <row r="662">
+      <c r="D662" s="39"/>
+    </row>
+    <row r="663">
+      <c r="D663" s="39"/>
+    </row>
+    <row r="664">
+      <c r="D664" s="39"/>
+    </row>
+    <row r="665">
+      <c r="D665" s="39"/>
+    </row>
+    <row r="666">
+      <c r="D666" s="39"/>
+    </row>
+    <row r="667">
+      <c r="D667" s="39"/>
+    </row>
+    <row r="668">
+      <c r="D668" s="39"/>
+    </row>
+    <row r="669">
+      <c r="D669" s="39"/>
+    </row>
+    <row r="670">
+      <c r="D670" s="39"/>
+    </row>
+    <row r="671">
+      <c r="D671" s="39"/>
+    </row>
+    <row r="672">
+      <c r="D672" s="39"/>
+    </row>
+    <row r="673">
+      <c r="D673" s="39"/>
+    </row>
+    <row r="674">
+      <c r="D674" s="39"/>
+    </row>
+    <row r="675">
+      <c r="D675" s="39"/>
+    </row>
+    <row r="676">
+      <c r="D676" s="39"/>
+    </row>
+    <row r="677">
+      <c r="D677" s="39"/>
+    </row>
+    <row r="678">
+      <c r="D678" s="39"/>
+    </row>
+    <row r="679">
+      <c r="D679" s="39"/>
+    </row>
+    <row r="680">
+      <c r="D680" s="39"/>
+    </row>
+    <row r="681">
+      <c r="D681" s="39"/>
+    </row>
+    <row r="682">
+      <c r="D682" s="39"/>
+    </row>
+    <row r="683">
+      <c r="D683" s="39"/>
+    </row>
+    <row r="684">
+      <c r="D684" s="39"/>
+    </row>
+    <row r="685">
+      <c r="D685" s="39"/>
+    </row>
+    <row r="686">
+      <c r="D686" s="39"/>
+    </row>
+    <row r="687">
+      <c r="D687" s="39"/>
+    </row>
+    <row r="688">
+      <c r="D688" s="39"/>
+    </row>
+    <row r="689">
+      <c r="D689" s="39"/>
+    </row>
+    <row r="690">
+      <c r="D690" s="39"/>
+    </row>
+    <row r="691">
+      <c r="D691" s="39"/>
+    </row>
+    <row r="692">
+      <c r="D692" s="39"/>
+    </row>
+    <row r="693">
+      <c r="D693" s="39"/>
+    </row>
+    <row r="694">
+      <c r="D694" s="39"/>
+    </row>
+    <row r="695">
+      <c r="D695" s="39"/>
+    </row>
+    <row r="696">
+      <c r="D696" s="39"/>
+    </row>
+    <row r="697">
+      <c r="D697" s="39"/>
+    </row>
+    <row r="698">
+      <c r="D698" s="39"/>
+    </row>
+    <row r="699">
+      <c r="D699" s="39"/>
+    </row>
+    <row r="700">
+      <c r="D700" s="39"/>
+    </row>
+    <row r="701">
+      <c r="D701" s="39"/>
+    </row>
+    <row r="702">
+      <c r="D702" s="39"/>
+    </row>
+    <row r="703">
+      <c r="D703" s="39"/>
+    </row>
+    <row r="704">
+      <c r="D704" s="39"/>
+    </row>
+    <row r="705">
+      <c r="D705" s="39"/>
+    </row>
+    <row r="706">
+      <c r="D706" s="39"/>
+    </row>
+    <row r="707">
+      <c r="D707" s="39"/>
+    </row>
+    <row r="708">
+      <c r="D708" s="39"/>
+    </row>
+    <row r="709">
+      <c r="D709" s="39"/>
+    </row>
+    <row r="710">
+      <c r="D710" s="39"/>
+    </row>
+    <row r="711">
+      <c r="D711" s="39"/>
+    </row>
+    <row r="712">
+      <c r="D712" s="39"/>
+    </row>
+    <row r="713">
+      <c r="D713" s="39"/>
+    </row>
+    <row r="714">
+      <c r="D714" s="39"/>
+    </row>
+    <row r="715">
+      <c r="D715" s="39"/>
+    </row>
+    <row r="716">
+      <c r="D716" s="39"/>
+    </row>
+    <row r="717">
+      <c r="D717" s="39"/>
+    </row>
+    <row r="718">
+      <c r="D718" s="39"/>
+    </row>
+    <row r="719">
+      <c r="D719" s="39"/>
+    </row>
+    <row r="720">
+      <c r="D720" s="39"/>
+    </row>
+    <row r="721">
+      <c r="D721" s="39"/>
+    </row>
+    <row r="722">
+      <c r="D722" s="39"/>
+    </row>
+    <row r="723">
+      <c r="D723" s="39"/>
+    </row>
+    <row r="724">
+      <c r="D724" s="39"/>
+    </row>
+    <row r="725">
+      <c r="D725" s="39"/>
+    </row>
+    <row r="726">
+      <c r="D726" s="39"/>
+    </row>
+    <row r="727">
+      <c r="D727" s="39"/>
+    </row>
+    <row r="728">
+      <c r="D728" s="39"/>
+    </row>
+    <row r="729">
+      <c r="D729" s="39"/>
+    </row>
+    <row r="730">
+      <c r="D730" s="39"/>
+    </row>
+    <row r="731">
+      <c r="D731" s="39"/>
+    </row>
+    <row r="732">
+      <c r="D732" s="39"/>
+    </row>
+    <row r="733">
+      <c r="D733" s="39"/>
+    </row>
+    <row r="734">
+      <c r="D734" s="39"/>
+    </row>
+    <row r="735">
+      <c r="D735" s="39"/>
+    </row>
+    <row r="736">
+      <c r="D736" s="39"/>
+    </row>
+    <row r="737">
+      <c r="D737" s="39"/>
+    </row>
+    <row r="738">
+      <c r="D738" s="39"/>
+    </row>
+    <row r="739">
+      <c r="D739" s="39"/>
+    </row>
+    <row r="740">
+      <c r="D740" s="39"/>
+    </row>
+    <row r="741">
+      <c r="D741" s="39"/>
+    </row>
+    <row r="742">
+      <c r="D742" s="39"/>
+    </row>
+    <row r="743">
+      <c r="D743" s="39"/>
+    </row>
+    <row r="744">
+      <c r="D744" s="39"/>
+    </row>
+    <row r="745">
+      <c r="D745" s="39"/>
+    </row>
+    <row r="746">
+      <c r="D746" s="39"/>
+    </row>
+    <row r="747">
+      <c r="D747" s="39"/>
+    </row>
+    <row r="748">
+      <c r="D748" s="39"/>
+    </row>
+    <row r="749">
+      <c r="D749" s="39"/>
+    </row>
+    <row r="750">
+      <c r="D750" s="39"/>
+    </row>
+    <row r="751">
+      <c r="D751" s="39"/>
+    </row>
+    <row r="752">
+      <c r="D752" s="39"/>
+    </row>
+    <row r="753">
+      <c r="D753" s="39"/>
+    </row>
+    <row r="754">
+      <c r="D754" s="39"/>
+    </row>
+    <row r="755">
+      <c r="D755" s="39"/>
+    </row>
+    <row r="756">
+      <c r="D756" s="39"/>
+    </row>
+    <row r="757">
+      <c r="D757" s="39"/>
+    </row>
+    <row r="758">
+      <c r="D758" s="39"/>
+    </row>
+    <row r="759">
+      <c r="D759" s="39"/>
+    </row>
+    <row r="760">
+      <c r="D760" s="39"/>
+    </row>
+    <row r="761">
+      <c r="D761" s="39"/>
+    </row>
+    <row r="762">
+      <c r="D762" s="39"/>
+    </row>
+    <row r="763">
+      <c r="D763" s="39"/>
+    </row>
+    <row r="764">
+      <c r="D764" s="39"/>
+    </row>
+    <row r="765">
+      <c r="D765" s="39"/>
+    </row>
+    <row r="766">
+      <c r="D766" s="39"/>
+    </row>
+    <row r="767">
+      <c r="D767" s="39"/>
+    </row>
+    <row r="768">
+      <c r="D768" s="39"/>
+    </row>
+    <row r="769">
+      <c r="D769" s="39"/>
+    </row>
+    <row r="770">
+      <c r="D770" s="39"/>
+    </row>
+    <row r="771">
+      <c r="D771" s="39"/>
+    </row>
+    <row r="772">
+      <c r="D772" s="39"/>
+    </row>
+    <row r="773">
+      <c r="D773" s="39"/>
+    </row>
+    <row r="774">
+      <c r="D774" s="39"/>
+    </row>
+    <row r="775">
+      <c r="D775" s="39"/>
+    </row>
+    <row r="776">
+      <c r="D776" s="39"/>
+    </row>
+    <row r="777">
+      <c r="D777" s="39"/>
+    </row>
+    <row r="778">
+      <c r="D778" s="39"/>
+    </row>
+    <row r="779">
+      <c r="D779" s="39"/>
+    </row>
+    <row r="780">
+      <c r="D780" s="39"/>
+    </row>
+    <row r="781">
+      <c r="D781" s="39"/>
+    </row>
+    <row r="782">
+      <c r="D782" s="39"/>
+    </row>
+    <row r="783">
+      <c r="D783" s="39"/>
+    </row>
+    <row r="784">
+      <c r="D784" s="39"/>
+    </row>
+    <row r="785">
+      <c r="D785" s="39"/>
+    </row>
+    <row r="786">
+      <c r="D786" s="39"/>
+    </row>
+    <row r="787">
+      <c r="D787" s="39"/>
+    </row>
+    <row r="788">
+      <c r="D788" s="39"/>
+    </row>
+    <row r="789">
+      <c r="D789" s="39"/>
+    </row>
+    <row r="790">
+      <c r="D790" s="39"/>
+    </row>
+    <row r="791">
+      <c r="D791" s="39"/>
+    </row>
+    <row r="792">
+      <c r="D792" s="39"/>
+    </row>
+    <row r="793">
+      <c r="D793" s="39"/>
+    </row>
+    <row r="794">
+      <c r="D794" s="39"/>
+    </row>
+    <row r="795">
+      <c r="D795" s="39"/>
+    </row>
+    <row r="796">
+      <c r="D796" s="39"/>
+    </row>
+    <row r="797">
+      <c r="D797" s="39"/>
+    </row>
+    <row r="798">
+      <c r="D798" s="39"/>
+    </row>
+    <row r="799">
+      <c r="D799" s="39"/>
+    </row>
+    <row r="800">
+      <c r="D800" s="39"/>
+    </row>
+    <row r="801">
+      <c r="D801" s="39"/>
+    </row>
+    <row r="802">
+      <c r="D802" s="39"/>
+    </row>
+    <row r="803">
+      <c r="D803" s="39"/>
+    </row>
+    <row r="804">
+      <c r="D804" s="39"/>
+    </row>
+    <row r="805">
+      <c r="D805" s="39"/>
+    </row>
+    <row r="806">
+      <c r="D806" s="39"/>
+    </row>
+    <row r="807">
+      <c r="D807" s="39"/>
+    </row>
+    <row r="808">
+      <c r="D808" s="39"/>
+    </row>
+    <row r="809">
+      <c r="D809" s="39"/>
+    </row>
+    <row r="810">
+      <c r="D810" s="39"/>
+    </row>
+    <row r="811">
+      <c r="D811" s="39"/>
+    </row>
+    <row r="812">
+      <c r="D812" s="39"/>
+    </row>
+    <row r="813">
+      <c r="D813" s="39"/>
+    </row>
+    <row r="814">
+      <c r="D814" s="39"/>
+    </row>
+    <row r="815">
+      <c r="D815" s="39"/>
+    </row>
+    <row r="816">
+      <c r="D816" s="39"/>
+    </row>
+    <row r="817">
+      <c r="D817" s="39"/>
+    </row>
+    <row r="818">
+      <c r="D818" s="39"/>
+    </row>
+    <row r="819">
+      <c r="D819" s="39"/>
+    </row>
+    <row r="820">
+      <c r="D820" s="39"/>
+    </row>
+    <row r="821">
+      <c r="D821" s="39"/>
+    </row>
+    <row r="822">
+      <c r="D822" s="39"/>
+    </row>
+    <row r="823">
+      <c r="D823" s="39"/>
+    </row>
+    <row r="824">
+      <c r="D824" s="39"/>
+    </row>
+    <row r="825">
+      <c r="D825" s="39"/>
+    </row>
+    <row r="826">
+      <c r="D826" s="39"/>
+    </row>
+    <row r="827">
+      <c r="D827" s="39"/>
+    </row>
+    <row r="828">
+      <c r="D828" s="39"/>
+    </row>
+    <row r="829">
+      <c r="D829" s="39"/>
+    </row>
+    <row r="830">
+      <c r="D830" s="39"/>
+    </row>
+    <row r="831">
+      <c r="D831" s="39"/>
+    </row>
+    <row r="832">
+      <c r="D832" s="39"/>
+    </row>
+    <row r="833">
+      <c r="D833" s="39"/>
+    </row>
+    <row r="834">
+      <c r="D834" s="39"/>
+    </row>
+    <row r="835">
+      <c r="D835" s="39"/>
+    </row>
+    <row r="836">
+      <c r="D836" s="39"/>
+    </row>
+    <row r="837">
+      <c r="D837" s="39"/>
+    </row>
+    <row r="838">
+      <c r="D838" s="39"/>
+    </row>
+    <row r="839">
+      <c r="D839" s="39"/>
+    </row>
+    <row r="840">
+      <c r="D840" s="39"/>
+    </row>
+    <row r="841">
+      <c r="D841" s="39"/>
+    </row>
+    <row r="842">
+      <c r="D842" s="39"/>
+    </row>
+    <row r="843">
+      <c r="D843" s="39"/>
+    </row>
+    <row r="844">
+      <c r="D844" s="39"/>
+    </row>
+    <row r="845">
+      <c r="D845" s="39"/>
+    </row>
+    <row r="846">
+      <c r="D846" s="39"/>
+    </row>
+    <row r="847">
+      <c r="D847" s="39"/>
+    </row>
+    <row r="848">
+      <c r="D848" s="39"/>
+    </row>
+    <row r="849">
+      <c r="D849" s="39"/>
+    </row>
+    <row r="850">
+      <c r="D850" s="39"/>
+    </row>
+    <row r="851">
+      <c r="D851" s="39"/>
+    </row>
+    <row r="852">
+      <c r="D852" s="39"/>
+    </row>
+    <row r="853">
+      <c r="D853" s="39"/>
+    </row>
+    <row r="854">
+      <c r="D854" s="39"/>
+    </row>
+    <row r="855">
+      <c r="D855" s="39"/>
+    </row>
+    <row r="856">
+      <c r="D856" s="39"/>
+    </row>
+    <row r="857">
+      <c r="D857" s="39"/>
+    </row>
+    <row r="858">
+      <c r="D858" s="39"/>
+    </row>
+    <row r="859">
+      <c r="D859" s="39"/>
+    </row>
+    <row r="860">
+      <c r="D860" s="39"/>
+    </row>
+    <row r="861">
+      <c r="D861" s="39"/>
+    </row>
+    <row r="862">
+      <c r="D862" s="39"/>
+    </row>
+    <row r="863">
+      <c r="D863" s="39"/>
+    </row>
+    <row r="864">
+      <c r="D864" s="39"/>
+    </row>
+    <row r="865">
+      <c r="D865" s="39"/>
+    </row>
+    <row r="866">
+      <c r="D866" s="39"/>
+    </row>
+    <row r="867">
+      <c r="D867" s="39"/>
+    </row>
+    <row r="868">
+      <c r="D868" s="39"/>
+    </row>
+    <row r="869">
+      <c r="D869" s="39"/>
+    </row>
+    <row r="870">
+      <c r="D870" s="39"/>
+    </row>
+    <row r="871">
+      <c r="D871" s="39"/>
+    </row>
+    <row r="872">
+      <c r="D872" s="39"/>
+    </row>
+    <row r="873">
+      <c r="D873" s="39"/>
+    </row>
+    <row r="874">
+      <c r="D874" s="39"/>
+    </row>
+    <row r="875">
+      <c r="D875" s="39"/>
+    </row>
+    <row r="876">
+      <c r="D876" s="39"/>
+    </row>
+    <row r="877">
+      <c r="D877" s="39"/>
+    </row>
+    <row r="878">
+      <c r="D878" s="39"/>
+    </row>
+    <row r="879">
+      <c r="D879" s="39"/>
+    </row>
+    <row r="880">
+      <c r="D880" s="39"/>
+    </row>
+    <row r="881">
+      <c r="D881" s="39"/>
+    </row>
+    <row r="882">
+      <c r="D882" s="39"/>
+    </row>
+    <row r="883">
+      <c r="D883" s="39"/>
+    </row>
+    <row r="884">
+      <c r="D884" s="39"/>
+    </row>
+    <row r="885">
+      <c r="D885" s="39"/>
+    </row>
+    <row r="886">
+      <c r="D886" s="39"/>
+    </row>
+    <row r="887">
+      <c r="D887" s="39"/>
+    </row>
+    <row r="888">
+      <c r="D888" s="39"/>
+    </row>
+    <row r="889">
+      <c r="D889" s="39"/>
+    </row>
+    <row r="890">
+      <c r="D890" s="39"/>
+    </row>
+    <row r="891">
+      <c r="D891" s="39"/>
+    </row>
+    <row r="892">
+      <c r="D892" s="39"/>
+    </row>
+    <row r="893">
+      <c r="D893" s="39"/>
+    </row>
+    <row r="894">
+      <c r="D894" s="39"/>
+    </row>
+    <row r="895">
+      <c r="D895" s="39"/>
+    </row>
+    <row r="896">
+      <c r="D896" s="39"/>
+    </row>
+    <row r="897">
+      <c r="D897" s="39"/>
+    </row>
+    <row r="898">
+      <c r="D898" s="39"/>
+    </row>
+    <row r="899">
+      <c r="D899" s="39"/>
+    </row>
+    <row r="900">
+      <c r="D900" s="39"/>
+    </row>
+    <row r="901">
+      <c r="D901" s="39"/>
+    </row>
+    <row r="902">
+      <c r="D902" s="39"/>
+    </row>
+    <row r="903">
+      <c r="D903" s="39"/>
+    </row>
+    <row r="904">
+      <c r="D904" s="39"/>
+    </row>
+    <row r="905">
+      <c r="D905" s="39"/>
+    </row>
+    <row r="906">
+      <c r="D906" s="39"/>
+    </row>
+    <row r="907">
+      <c r="D907" s="39"/>
+    </row>
+    <row r="908">
+      <c r="D908" s="39"/>
+    </row>
+    <row r="909">
+      <c r="D909" s="39"/>
+    </row>
+    <row r="910">
+      <c r="D910" s="39"/>
+    </row>
+    <row r="911">
+      <c r="D911" s="39"/>
+    </row>
+    <row r="912">
+      <c r="D912" s="39"/>
+    </row>
+    <row r="913">
+      <c r="D913" s="39"/>
+    </row>
+    <row r="914">
+      <c r="D914" s="39"/>
+    </row>
+    <row r="915">
+      <c r="D915" s="39"/>
+    </row>
+    <row r="916">
+      <c r="D916" s="39"/>
+    </row>
+    <row r="917">
+      <c r="D917" s="39"/>
+    </row>
+    <row r="918">
+      <c r="D918" s="39"/>
+    </row>
+    <row r="919">
+      <c r="D919" s="39"/>
+    </row>
+    <row r="920">
+      <c r="D920" s="39"/>
+    </row>
+    <row r="921">
+      <c r="D921" s="39"/>
+    </row>
+    <row r="922">
+      <c r="D922" s="39"/>
+    </row>
+    <row r="923">
+      <c r="D923" s="39"/>
+    </row>
+    <row r="924">
+      <c r="D924" s="39"/>
+    </row>
+    <row r="925">
+      <c r="D925" s="39"/>
+    </row>
+    <row r="926">
+      <c r="D926" s="39"/>
+    </row>
+    <row r="927">
+      <c r="D927" s="39"/>
+    </row>
+    <row r="928">
+      <c r="D928" s="39"/>
+    </row>
+    <row r="929">
+      <c r="D929" s="39"/>
+    </row>
+    <row r="930">
+      <c r="D930" s="39"/>
+    </row>
+    <row r="931">
+      <c r="D931" s="39"/>
+    </row>
+    <row r="932">
+      <c r="D932" s="39"/>
+    </row>
+    <row r="933">
+      <c r="D933" s="39"/>
+    </row>
+    <row r="934">
+      <c r="D934" s="39"/>
+    </row>
+    <row r="935">
+      <c r="D935" s="39"/>
+    </row>
+    <row r="936">
+      <c r="D936" s="39"/>
+    </row>
+    <row r="937">
+      <c r="D937" s="39"/>
+    </row>
+    <row r="938">
+      <c r="D938" s="39"/>
+    </row>
+    <row r="939">
+      <c r="D939" s="39"/>
+    </row>
+    <row r="940">
+      <c r="D940" s="39"/>
+    </row>
+    <row r="941">
+      <c r="D941" s="39"/>
+    </row>
+    <row r="942">
+      <c r="D942" s="39"/>
+    </row>
+    <row r="943">
+      <c r="D943" s="39"/>
+    </row>
+    <row r="944">
+      <c r="D944" s="39"/>
+    </row>
+    <row r="945">
+      <c r="D945" s="39"/>
+    </row>
+    <row r="946">
+      <c r="D946" s="39"/>
+    </row>
+    <row r="947">
+      <c r="D947" s="39"/>
+    </row>
+    <row r="948">
+      <c r="D948" s="39"/>
+    </row>
+    <row r="949">
+      <c r="D949" s="39"/>
+    </row>
+    <row r="950">
+      <c r="D950" s="39"/>
+    </row>
+    <row r="951">
+      <c r="D951" s="39"/>
+    </row>
+    <row r="952">
+      <c r="D952" s="39"/>
+    </row>
+    <row r="953">
+      <c r="D953" s="39"/>
+    </row>
+    <row r="954">
+      <c r="D954" s="39"/>
+    </row>
+    <row r="955">
+      <c r="D955" s="39"/>
+    </row>
+    <row r="956">
+      <c r="D956" s="39"/>
+    </row>
+    <row r="957">
+      <c r="D957" s="39"/>
+    </row>
+    <row r="958">
+      <c r="D958" s="39"/>
+    </row>
+    <row r="959">
+      <c r="D959" s="39"/>
+    </row>
+    <row r="960">
+      <c r="D960" s="39"/>
+    </row>
+    <row r="961">
+      <c r="D961" s="39"/>
+    </row>
+    <row r="962">
+      <c r="D962" s="39"/>
+    </row>
+    <row r="963">
+      <c r="D963" s="39"/>
+    </row>
+    <row r="964">
+      <c r="D964" s="39"/>
+    </row>
+    <row r="965">
+      <c r="D965" s="39"/>
+    </row>
+    <row r="966">
+      <c r="D966" s="39"/>
+    </row>
+    <row r="967">
+      <c r="D967" s="39"/>
+    </row>
+    <row r="968">
+      <c r="D968" s="39"/>
+    </row>
+    <row r="969">
+      <c r="D969" s="39"/>
+    </row>
+    <row r="970">
+      <c r="D970" s="39"/>
+    </row>
+    <row r="971">
+      <c r="D971" s="39"/>
+    </row>
+    <row r="972">
+      <c r="D972" s="39"/>
+    </row>
+    <row r="973">
+      <c r="D973" s="39"/>
+    </row>
+    <row r="974">
+      <c r="D974" s="39"/>
+    </row>
+    <row r="975">
+      <c r="D975" s="39"/>
+    </row>
+    <row r="976">
+      <c r="D976" s="39"/>
+    </row>
+    <row r="977">
+      <c r="D977" s="39"/>
+    </row>
+    <row r="978">
+      <c r="D978" s="39"/>
+    </row>
+    <row r="979">
+      <c r="D979" s="39"/>
+    </row>
+    <row r="980">
+      <c r="D980" s="39"/>
+    </row>
+    <row r="981">
+      <c r="D981" s="39"/>
+    </row>
+    <row r="982">
+      <c r="D982" s="39"/>
+    </row>
+    <row r="983">
+      <c r="D983" s="39"/>
+    </row>
+    <row r="984">
+      <c r="D984" s="39"/>
+    </row>
+    <row r="985">
+      <c r="D985" s="39"/>
+    </row>
+    <row r="986">
+      <c r="D986" s="39"/>
+    </row>
+    <row r="987">
+      <c r="D987" s="39"/>
+    </row>
+    <row r="988">
+      <c r="D988" s="39"/>
+    </row>
+    <row r="989">
+      <c r="D989" s="39"/>
+    </row>
+    <row r="990">
+      <c r="D990" s="39"/>
+    </row>
+    <row r="991">
+      <c r="D991" s="39"/>
+    </row>
+    <row r="992">
+      <c r="D992" s="39"/>
+    </row>
+    <row r="993">
+      <c r="D993" s="39"/>
+    </row>
+    <row r="994">
+      <c r="D994" s="39"/>
+    </row>
+    <row r="995">
+      <c r="D995" s="39"/>
+    </row>
+    <row r="996">
+      <c r="D996" s="39"/>
+    </row>
+    <row r="997">
+      <c r="D997" s="39"/>
+    </row>
+    <row r="998">
+      <c r="D998" s="39"/>
+    </row>
+    <row r="999">
+      <c r="D999" s="39"/>
+    </row>
+    <row r="1000">
+      <c r="D1000" s="39"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>